--- a/复盘专用.xlsx
+++ b/复盘专用.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$356</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1545" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="465">
   <si>
     <t>旧数据</t>
   </si>
@@ -1381,6 +1381,24 @@
   </si>
   <si>
     <t>8月9日对话</t>
+  </si>
+  <si>
+    <t>班菲尔德</t>
+  </si>
+  <si>
+    <t>贝尔格拉诺</t>
+  </si>
+  <si>
+    <t>科尔多瓦中</t>
+  </si>
+  <si>
+    <t>亚冠精英</t>
+  </si>
+  <si>
+    <t>阿德莱德联</t>
+  </si>
+  <si>
+    <t>河内公安</t>
   </si>
   <si>
     <t>东京绿茵 +0/0.5</t>
@@ -2579,7 +2597,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N347"/>
+  <dimension ref="A1:N357"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="2"/>
@@ -9379,9 +9397,419 @@
         <v>449</v>
       </c>
     </row>
+    <row r="348" spans="1:14">
+      <c r="A348" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B348" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C348" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F348">
+        <v>1</v>
+      </c>
+      <c r="G348">
+        <v>13</v>
+      </c>
+      <c r="H348" t="s">
+        <v>9</v>
+      </c>
+      <c r="I348">
+        <v>0.95</v>
+      </c>
+      <c r="J348">
+        <v>0.94</v>
+      </c>
+      <c r="K348" t="s">
+        <v>448</v>
+      </c>
+      <c r="L348">
+        <v>0.91</v>
+      </c>
+      <c r="M348">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="349" spans="1:14">
+      <c r="A349" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B349" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F349">
+        <v>9</v>
+      </c>
+      <c r="G349">
+        <v>3</v>
+      </c>
+      <c r="H349" t="s">
+        <v>222</v>
+      </c>
+      <c r="I349">
+        <v>0.97</v>
+      </c>
+      <c r="J349">
+        <v>0.92</v>
+      </c>
+      <c r="K349">
+        <v>3</v>
+      </c>
+      <c r="L349">
+        <v>0.9</v>
+      </c>
+      <c r="M349">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="350" spans="1:14">
+      <c r="A350" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B350" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C350" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F350">
+        <v>23</v>
+      </c>
+      <c r="G350">
+        <v>8</v>
+      </c>
+      <c r="H350" t="s">
+        <v>164</v>
+      </c>
+      <c r="I350">
+        <v>1.08</v>
+      </c>
+      <c r="J350">
+        <v>0.77</v>
+      </c>
+      <c r="K350">
+        <v>2</v>
+      </c>
+      <c r="L350">
+        <v>0.9</v>
+      </c>
+      <c r="M350">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="351" spans="1:14">
+      <c r="A351" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B351" s="5">
+        <v>0.34375</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F351">
+        <v>15</v>
+      </c>
+      <c r="G351">
+        <v>25</v>
+      </c>
+      <c r="H351" t="s">
+        <v>34</v>
+      </c>
+      <c r="I351">
+        <v>0.96</v>
+      </c>
+      <c r="J351">
+        <v>0.93</v>
+      </c>
+      <c r="K351" t="s">
+        <v>443</v>
+      </c>
+      <c r="L351">
+        <v>0.88</v>
+      </c>
+      <c r="M351">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="352" spans="1:14">
+      <c r="A352" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B352" s="5">
+        <v>0.729166666666667</v>
+      </c>
+      <c r="C352" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="F352">
+        <v>2</v>
+      </c>
+      <c r="G352">
+        <v>1</v>
+      </c>
+      <c r="H352" t="s">
+        <v>166</v>
+      </c>
+      <c r="I352">
+        <v>1.02</v>
+      </c>
+      <c r="J352">
+        <v>0.8</v>
+      </c>
+      <c r="K352" t="s">
+        <v>447</v>
+      </c>
+      <c r="L352">
+        <v>0.86</v>
+      </c>
+      <c r="M352">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13">
+      <c r="A353" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B353" s="5">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="C353" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F353">
+        <v>4</v>
+      </c>
+      <c r="G353">
+        <v>4</v>
+      </c>
+      <c r="H353" t="s">
+        <v>65</v>
+      </c>
+      <c r="I353">
+        <v>1</v>
+      </c>
+      <c r="J353">
+        <v>0.82</v>
+      </c>
+      <c r="K353" t="s">
+        <v>443</v>
+      </c>
+      <c r="L353">
+        <v>0.95</v>
+      </c>
+      <c r="M353">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13">
+      <c r="A354" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B354" s="5">
+        <v>0</v>
+      </c>
+      <c r="C354" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="F354">
+        <v>1</v>
+      </c>
+      <c r="G354">
+        <v>1</v>
+      </c>
+      <c r="H354" t="s">
+        <v>166</v>
+      </c>
+      <c r="I354">
+        <v>1.05</v>
+      </c>
+      <c r="J354">
+        <v>0.84</v>
+      </c>
+      <c r="K354">
+        <v>3</v>
+      </c>
+      <c r="L354">
+        <v>0.94</v>
+      </c>
+      <c r="M354">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13">
+      <c r="A355" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B355" s="5">
+        <v>0</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F355">
+        <v>3</v>
+      </c>
+      <c r="G355">
+        <v>1</v>
+      </c>
+      <c r="H355" t="s">
+        <v>166</v>
+      </c>
+      <c r="I355">
+        <v>0.93</v>
+      </c>
+      <c r="J355">
+        <v>0.89</v>
+      </c>
+      <c r="K355" t="s">
+        <v>443</v>
+      </c>
+      <c r="L355">
+        <v>0.86</v>
+      </c>
+      <c r="M355">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="356" spans="1:13">
+      <c r="A356" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B356" s="5">
+        <v>0.0625</v>
+      </c>
+      <c r="C356" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F356">
+        <v>12</v>
+      </c>
+      <c r="G356">
+        <v>2</v>
+      </c>
+      <c r="H356" t="s">
+        <v>65</v>
+      </c>
+      <c r="I356">
+        <v>1.09</v>
+      </c>
+      <c r="J356">
+        <v>0.8</v>
+      </c>
+      <c r="K356">
+        <v>2.5</v>
+      </c>
+      <c r="L356">
+        <v>0.85</v>
+      </c>
+      <c r="M356">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="357" spans="1:13">
+      <c r="A357" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B357" s="5">
+        <v>0.0625</v>
+      </c>
+      <c r="C357" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F357">
+        <v>4</v>
+      </c>
+      <c r="G357">
+        <v>4</v>
+      </c>
+      <c r="H357" t="s">
+        <v>222</v>
+      </c>
+      <c r="I357">
+        <v>0.76</v>
+      </c>
+      <c r="J357">
+        <v>0.94</v>
+      </c>
+      <c r="K357">
+        <v>2.5</v>
+      </c>
+      <c r="L357">
+        <v>0.91</v>
+      </c>
+      <c r="M357">
+        <v>0.89</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E347" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E347">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E356" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:E356">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9703,7 +10131,7 @@
         <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -9720,7 +10148,7 @@
         <v>418</v>
       </c>
       <c r="E19" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -9737,7 +10165,7 @@
         <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -9754,7 +10182,7 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -9771,7 +10199,7 @@
         <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -9788,7 +10216,7 @@
         <v>421</v>
       </c>
       <c r="E23" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -9805,7 +10233,7 @@
         <v>427</v>
       </c>
       <c r="E24" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -9822,7 +10250,7 @@
         <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9839,7 +10267,7 @@
         <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>

--- a/复盘专用.xlsx
+++ b/复盘专用.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$356</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$357</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="465">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="469">
   <si>
     <t>旧数据</t>
   </si>
@@ -1399,6 +1399,18 @@
   </si>
   <si>
     <t>河内公安</t>
+  </si>
+  <si>
+    <t>南美杯</t>
+  </si>
+  <si>
+    <t>布拉干蒂诺RB</t>
+  </si>
+  <si>
+    <t>西恩夏诺</t>
+  </si>
+  <si>
+    <t>博塔弗戈</t>
   </si>
   <si>
     <t>东京绿茵 +0/0.5</t>
@@ -2597,7 +2609,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N357"/>
+  <dimension ref="A1:N367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="2"/>
@@ -9807,9 +9819,419 @@
         <v>0.89</v>
       </c>
     </row>
+    <row r="358" spans="1:13">
+      <c r="A358" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B358" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C358" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F358">
+        <v>8</v>
+      </c>
+      <c r="G358">
+        <v>11</v>
+      </c>
+      <c r="H358" t="s">
+        <v>39</v>
+      </c>
+      <c r="I358">
+        <v>1.07</v>
+      </c>
+      <c r="J358">
+        <v>0.82</v>
+      </c>
+      <c r="K358" t="s">
+        <v>443</v>
+      </c>
+      <c r="L358">
+        <v>0.84</v>
+      </c>
+      <c r="M358">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13">
+      <c r="A359" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B359" s="5">
+        <v>0</v>
+      </c>
+      <c r="C359" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F359">
+        <v>10</v>
+      </c>
+      <c r="G359">
+        <v>3</v>
+      </c>
+      <c r="H359" t="s">
+        <v>161</v>
+      </c>
+      <c r="I359">
+        <v>0.82</v>
+      </c>
+      <c r="J359">
+        <v>1</v>
+      </c>
+      <c r="K359">
+        <v>2.5</v>
+      </c>
+      <c r="L359">
+        <v>0.8</v>
+      </c>
+      <c r="M359">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:13">
+      <c r="A360" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B360" s="5">
+        <v>0</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F360">
+        <v>2</v>
+      </c>
+      <c r="G360">
+        <v>9</v>
+      </c>
+      <c r="H360" t="s">
+        <v>199</v>
+      </c>
+      <c r="I360">
+        <v>0.97</v>
+      </c>
+      <c r="J360">
+        <v>0.85</v>
+      </c>
+      <c r="K360">
+        <v>3</v>
+      </c>
+      <c r="L360">
+        <v>0.8</v>
+      </c>
+      <c r="M360">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:13">
+      <c r="A361" s="3">
+        <v>46246</v>
+      </c>
+      <c r="B361" s="5">
+        <v>0</v>
+      </c>
+      <c r="C361" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F361">
+        <v>2</v>
+      </c>
+      <c r="G361">
+        <v>4</v>
+      </c>
+      <c r="H361" t="s">
+        <v>403</v>
+      </c>
+      <c r="I361">
+        <v>0.85</v>
+      </c>
+      <c r="J361">
+        <v>0.97</v>
+      </c>
+      <c r="K361" t="s">
+        <v>445</v>
+      </c>
+      <c r="L361">
+        <v>0.99</v>
+      </c>
+      <c r="M361">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="362" spans="1:13">
+      <c r="A362" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B362" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F362">
+        <v>16</v>
+      </c>
+      <c r="G362">
+        <v>9</v>
+      </c>
+      <c r="H362" t="s">
+        <v>161</v>
+      </c>
+      <c r="I362">
+        <v>1.16</v>
+      </c>
+      <c r="J362">
+        <v>0.75</v>
+      </c>
+      <c r="K362">
+        <v>2.5</v>
+      </c>
+      <c r="L362">
+        <v>0.98</v>
+      </c>
+      <c r="M362">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13">
+      <c r="A363" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B363" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F363">
+        <v>3</v>
+      </c>
+      <c r="G363">
+        <v>12</v>
+      </c>
+      <c r="H363" t="s">
+        <v>161</v>
+      </c>
+      <c r="I363">
+        <v>0.99</v>
+      </c>
+      <c r="J363">
+        <v>0.83</v>
+      </c>
+      <c r="K363">
+        <v>2.5</v>
+      </c>
+      <c r="L363">
+        <v>0.93</v>
+      </c>
+      <c r="M363">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="364" spans="1:13">
+      <c r="A364" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B364" s="5">
+        <v>0.0208333333333333</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F364">
+        <v>1</v>
+      </c>
+      <c r="G364">
+        <v>2</v>
+      </c>
+      <c r="H364" t="s">
+        <v>161</v>
+      </c>
+      <c r="I364">
+        <v>0.79</v>
+      </c>
+      <c r="J364">
+        <v>1.03</v>
+      </c>
+      <c r="K364" t="s">
+        <v>443</v>
+      </c>
+      <c r="L364">
+        <v>0.92</v>
+      </c>
+      <c r="M364">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="365" spans="1:13">
+      <c r="A365" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B365" s="5">
+        <v>0</v>
+      </c>
+      <c r="C365" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F365">
+        <v>2</v>
+      </c>
+      <c r="G365">
+        <v>9</v>
+      </c>
+      <c r="H365" t="s">
+        <v>199</v>
+      </c>
+      <c r="I365">
+        <v>0.82</v>
+      </c>
+      <c r="J365">
+        <v>0.88</v>
+      </c>
+      <c r="K365">
+        <v>3</v>
+      </c>
+      <c r="L365">
+        <v>0.84</v>
+      </c>
+      <c r="M365">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13">
+      <c r="A366" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B366" s="5">
+        <v>0</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F366">
+        <v>2</v>
+      </c>
+      <c r="G366">
+        <v>4</v>
+      </c>
+      <c r="H366" t="s">
+        <v>403</v>
+      </c>
+      <c r="I366">
+        <v>0.91</v>
+      </c>
+      <c r="J366">
+        <v>0.79</v>
+      </c>
+      <c r="K366" t="s">
+        <v>445</v>
+      </c>
+      <c r="L366">
+        <v>0.99</v>
+      </c>
+      <c r="M366">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="367" spans="1:13">
+      <c r="A367" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B367" s="5">
+        <v>0</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F367">
+        <v>10</v>
+      </c>
+      <c r="G367">
+        <v>3</v>
+      </c>
+      <c r="H367" t="s">
+        <v>161</v>
+      </c>
+      <c r="I367">
+        <v>0.73</v>
+      </c>
+      <c r="J367">
+        <v>0.97</v>
+      </c>
+      <c r="K367" t="s">
+        <v>443</v>
+      </c>
+      <c r="L367">
+        <v>0.79</v>
+      </c>
+      <c r="M367">
+        <v>0.91</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E356" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E356">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E357" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:E357">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9822,7 +10244,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -10131,7 +10553,7 @@
         <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -10148,7 +10570,7 @@
         <v>418</v>
       </c>
       <c r="E19" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -10165,7 +10587,7 @@
         <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -10182,7 +10604,7 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -10199,7 +10621,7 @@
         <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -10216,7 +10638,7 @@
         <v>421</v>
       </c>
       <c r="E23" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -10233,7 +10655,7 @@
         <v>427</v>
       </c>
       <c r="E24" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -10250,7 +10672,7 @@
         <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -10267,7 +10689,177 @@
         <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>464</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B27" t="s">
+        <v>456</v>
+      </c>
+      <c r="C27" t="s">
+        <v>457</v>
+      </c>
+      <c r="D27" t="s">
+        <v>195</v>
+      </c>
+      <c r="E27" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B28" t="s">
+        <v>181</v>
+      </c>
+      <c r="C28" t="s">
+        <v>242</v>
+      </c>
+      <c r="D28" t="s">
+        <v>241</v>
+      </c>
+      <c r="E28" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B29" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" t="s">
+        <v>221</v>
+      </c>
+      <c r="D29" t="s">
+        <v>220</v>
+      </c>
+      <c r="E29" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>46246</v>
+      </c>
+      <c r="B30" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E30" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B31" t="s">
+        <v>456</v>
+      </c>
+      <c r="C31" t="s">
+        <v>458</v>
+      </c>
+      <c r="D31" t="s">
+        <v>459</v>
+      </c>
+      <c r="E31" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B32" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" t="s">
+        <v>138</v>
+      </c>
+      <c r="D32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B33" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" t="s">
+        <v>205</v>
+      </c>
+      <c r="D33" t="s">
+        <v>204</v>
+      </c>
+      <c r="E33" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B34" t="s">
+        <v>181</v>
+      </c>
+      <c r="C34" t="s">
+        <v>221</v>
+      </c>
+      <c r="D34" t="s">
+        <v>220</v>
+      </c>
+      <c r="E34" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B35" t="s">
+        <v>181</v>
+      </c>
+      <c r="C35" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" t="s">
+        <v>208</v>
+      </c>
+      <c r="E35" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
+        <v>46247</v>
+      </c>
+      <c r="B36" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" t="s">
+        <v>242</v>
+      </c>
+      <c r="D36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E36" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/复盘专用.xlsx
+++ b/复盘专用.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$367</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1675" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="477">
   <si>
     <t>旧数据</t>
   </si>
@@ -1411,6 +1411,30 @@
   </si>
   <si>
     <t>博塔弗戈</t>
+  </si>
+  <si>
+    <t>柏太阳神</t>
+  </si>
+  <si>
+    <t>竞技俱乐部</t>
+  </si>
+  <si>
+    <t>长崎成功丸</t>
+  </si>
+  <si>
+    <t>亨克</t>
+  </si>
+  <si>
+    <t>旧海弗莱鲁汶</t>
+  </si>
+  <si>
+    <t>弗鲁米嫩塞</t>
+  </si>
+  <si>
+    <t>格雷米奥</t>
+  </si>
+  <si>
+    <t>沙勒罗瓦</t>
   </si>
   <si>
     <t>东京绿茵 +0/0.5</t>
@@ -2609,7 +2633,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N367"/>
+  <dimension ref="A1:N394"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="2"/>
@@ -10229,9 +10253,1116 @@
         <v>0.91</v>
       </c>
     </row>
+    <row r="368" spans="1:13">
+      <c r="A368" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B368" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F368">
+        <v>10</v>
+      </c>
+      <c r="G368">
+        <v>6</v>
+      </c>
+      <c r="H368" t="s">
+        <v>222</v>
+      </c>
+      <c r="I368">
+        <v>0.99</v>
+      </c>
+      <c r="J368">
+        <v>0.9</v>
+      </c>
+      <c r="K368" t="s">
+        <v>443</v>
+      </c>
+      <c r="L368">
+        <v>1.06</v>
+      </c>
+      <c r="M368">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="369" spans="1:13">
+      <c r="A369" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B369" s="5">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F369">
+        <v>4</v>
+      </c>
+      <c r="G369">
+        <v>8</v>
+      </c>
+      <c r="H369" t="s">
+        <v>166</v>
+      </c>
+      <c r="I369">
+        <v>1.04</v>
+      </c>
+      <c r="J369">
+        <v>0.85</v>
+      </c>
+      <c r="K369" t="s">
+        <v>447</v>
+      </c>
+      <c r="L369">
+        <v>1</v>
+      </c>
+      <c r="M369">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="370" spans="1:13">
+      <c r="A370" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B370" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F370">
+        <v>9</v>
+      </c>
+      <c r="G370">
+        <v>2</v>
+      </c>
+      <c r="H370" t="s">
+        <v>161</v>
+      </c>
+      <c r="I370">
+        <v>0.82</v>
+      </c>
+      <c r="J370">
+        <v>1.07</v>
+      </c>
+      <c r="K370" t="s">
+        <v>448</v>
+      </c>
+      <c r="L370">
+        <v>0.86</v>
+      </c>
+      <c r="M370">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13">
+      <c r="A371" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B371" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F371">
+        <v>7</v>
+      </c>
+      <c r="G371">
+        <v>6</v>
+      </c>
+      <c r="H371" t="s">
+        <v>161</v>
+      </c>
+      <c r="I371">
+        <v>0.85</v>
+      </c>
+      <c r="J371">
+        <v>1.04</v>
+      </c>
+      <c r="K371" t="s">
+        <v>447</v>
+      </c>
+      <c r="L371">
+        <v>0.91</v>
+      </c>
+      <c r="M371">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="372" spans="1:13">
+      <c r="A372" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B372" s="5">
+        <v>0.114583333333333</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F372">
+        <v>8</v>
+      </c>
+      <c r="G372">
+        <v>11</v>
+      </c>
+      <c r="H372" t="s">
+        <v>161</v>
+      </c>
+      <c r="I372">
+        <v>0.88</v>
+      </c>
+      <c r="J372">
+        <v>1.01</v>
+      </c>
+      <c r="K372" t="s">
+        <v>447</v>
+      </c>
+      <c r="L372">
+        <v>0.95</v>
+      </c>
+      <c r="M372">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="373" spans="1:13">
+      <c r="A373" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B373" s="5">
+        <v>0.3125</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F373">
+        <v>16</v>
+      </c>
+      <c r="G373">
+        <v>23</v>
+      </c>
+      <c r="H373" t="s">
+        <v>39</v>
+      </c>
+      <c r="I373">
+        <v>0.82</v>
+      </c>
+      <c r="J373">
+        <v>1.07</v>
+      </c>
+      <c r="K373">
+        <v>2</v>
+      </c>
+      <c r="L373">
+        <v>0.82</v>
+      </c>
+      <c r="M373">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13">
+      <c r="A374" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B374" s="5">
+        <v>0.708333333333333</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F374">
+        <v>4</v>
+      </c>
+      <c r="G374">
+        <v>17</v>
+      </c>
+      <c r="H374" t="s">
+        <v>39</v>
+      </c>
+      <c r="I374">
+        <v>0.94</v>
+      </c>
+      <c r="J374">
+        <v>0.95</v>
+      </c>
+      <c r="K374">
+        <v>2.5</v>
+      </c>
+      <c r="L374">
+        <v>0.92</v>
+      </c>
+      <c r="M374">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="375" spans="1:13">
+      <c r="A375" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B375" s="5">
+        <v>0.746527777777778</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F375">
+        <v>16</v>
+      </c>
+      <c r="G375">
+        <v>7</v>
+      </c>
+      <c r="H375" t="s">
+        <v>161</v>
+      </c>
+      <c r="I375">
+        <v>0.96</v>
+      </c>
+      <c r="J375">
+        <v>0.93</v>
+      </c>
+      <c r="K375" t="s">
+        <v>443</v>
+      </c>
+      <c r="L375">
+        <v>0.85</v>
+      </c>
+      <c r="M375">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="376" spans="1:13">
+      <c r="A376" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B376" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="F376">
+        <v>19</v>
+      </c>
+      <c r="G376">
+        <v>2</v>
+      </c>
+      <c r="H376" t="s">
+        <v>222</v>
+      </c>
+      <c r="I376">
+        <v>0.93</v>
+      </c>
+      <c r="J376">
+        <v>0.96</v>
+      </c>
+      <c r="K376" t="s">
+        <v>443</v>
+      </c>
+      <c r="L376">
+        <v>0.98</v>
+      </c>
+      <c r="M376">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:13">
+      <c r="A377" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B377" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F377">
+        <v>12</v>
+      </c>
+      <c r="G377">
+        <v>3</v>
+      </c>
+      <c r="H377" t="s">
+        <v>40</v>
+      </c>
+      <c r="I377">
+        <v>1.01</v>
+      </c>
+      <c r="J377">
+        <v>0.88</v>
+      </c>
+      <c r="K377">
+        <v>2.5</v>
+      </c>
+      <c r="L377">
+        <v>0.88</v>
+      </c>
+      <c r="M377">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:13">
+      <c r="A378" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B378" s="5">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F378">
+        <v>1</v>
+      </c>
+      <c r="G378">
+        <v>9</v>
+      </c>
+      <c r="H378" t="s">
+        <v>39</v>
+      </c>
+      <c r="I378">
+        <v>1</v>
+      </c>
+      <c r="J378">
+        <v>0.89</v>
+      </c>
+      <c r="K378">
+        <v>2.5</v>
+      </c>
+      <c r="L378">
+        <v>0.91</v>
+      </c>
+      <c r="M378">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13">
+      <c r="A379" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B379" s="5">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E379" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F379">
+        <v>12</v>
+      </c>
+      <c r="G379">
+        <v>4</v>
+      </c>
+      <c r="H379" t="s">
+        <v>40</v>
+      </c>
+      <c r="I379">
+        <v>0.84</v>
+      </c>
+      <c r="J379">
+        <v>1.05</v>
+      </c>
+      <c r="K379" t="s">
+        <v>447</v>
+      </c>
+      <c r="L379">
+        <v>0.81</v>
+      </c>
+      <c r="M379">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="380" spans="1:13">
+      <c r="A380" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B380" s="5">
+        <v>0.114583333333333</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E380" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="F380">
+        <v>1</v>
+      </c>
+      <c r="G380">
+        <v>18</v>
+      </c>
+      <c r="H380" t="s">
+        <v>166</v>
+      </c>
+      <c r="I380">
+        <v>0.86</v>
+      </c>
+      <c r="J380">
+        <v>1.03</v>
+      </c>
+      <c r="K380">
+        <v>3.5</v>
+      </c>
+      <c r="L380">
+        <v>0.97</v>
+      </c>
+      <c r="M380">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="381" spans="1:13">
+      <c r="A381" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B381" s="5">
+        <v>0.114583333333333</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E381" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F381">
+        <v>15</v>
+      </c>
+      <c r="G381">
+        <v>2</v>
+      </c>
+      <c r="H381" t="s">
+        <v>178</v>
+      </c>
+      <c r="I381">
+        <v>0.82</v>
+      </c>
+      <c r="J381">
+        <v>1.07</v>
+      </c>
+      <c r="K381" t="s">
+        <v>448</v>
+      </c>
+      <c r="L381">
+        <v>0.98</v>
+      </c>
+      <c r="M381">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="382" spans="1:13">
+      <c r="A382" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B382" s="5">
+        <v>0.145833333333333</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E382" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="F382">
+        <v>4</v>
+      </c>
+      <c r="G382">
+        <v>1</v>
+      </c>
+      <c r="H382" t="s">
+        <v>65</v>
+      </c>
+      <c r="I382">
+        <v>1.09</v>
+      </c>
+      <c r="J382">
+        <v>0.8</v>
+      </c>
+      <c r="K382" t="s">
+        <v>443</v>
+      </c>
+      <c r="L382">
+        <v>1.05</v>
+      </c>
+      <c r="M382">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="383" spans="1:13">
+      <c r="A383" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B383" s="5">
+        <v>0</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E383" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F383">
+        <v>12</v>
+      </c>
+      <c r="G383">
+        <v>10</v>
+      </c>
+      <c r="H383" t="s">
+        <v>26</v>
+      </c>
+      <c r="I383">
+        <v>0.8</v>
+      </c>
+      <c r="J383">
+        <v>1.09</v>
+      </c>
+      <c r="K383" t="s">
+        <v>448</v>
+      </c>
+      <c r="L383">
+        <v>0.94</v>
+      </c>
+      <c r="M383">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="384" spans="1:13">
+      <c r="A384" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B384" s="5">
+        <v>0.0104166666666667</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E384" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F384">
+        <v>17</v>
+      </c>
+      <c r="G384">
+        <v>7</v>
+      </c>
+      <c r="H384" t="s">
+        <v>65</v>
+      </c>
+      <c r="I384">
+        <v>0.92</v>
+      </c>
+      <c r="J384">
+        <v>0.97</v>
+      </c>
+      <c r="K384">
+        <v>2.5</v>
+      </c>
+      <c r="L384">
+        <v>1.04</v>
+      </c>
+      <c r="M384">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13">
+      <c r="A385" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B385" s="5">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="C385" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E385" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F385">
+        <v>8</v>
+      </c>
+      <c r="G385">
+        <v>1</v>
+      </c>
+      <c r="H385" t="s">
+        <v>65</v>
+      </c>
+      <c r="I385">
+        <v>1.06</v>
+      </c>
+      <c r="J385">
+        <v>0.83</v>
+      </c>
+      <c r="K385">
+        <v>2.5</v>
+      </c>
+      <c r="L385">
+        <v>0.93</v>
+      </c>
+      <c r="M385">
+        <v>0.94</v>
+      </c>
+    </row>
+    <row r="386" spans="1:13">
+      <c r="A386" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B386" s="5">
+        <v>0.229166666666667</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E386" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F386">
+        <v>15</v>
+      </c>
+      <c r="G386">
+        <v>2</v>
+      </c>
+      <c r="H386" t="s">
+        <v>40</v>
+      </c>
+      <c r="I386">
+        <v>0.96</v>
+      </c>
+      <c r="J386">
+        <v>0.93</v>
+      </c>
+      <c r="K386">
+        <v>2.5</v>
+      </c>
+      <c r="L386">
+        <v>1.04</v>
+      </c>
+      <c r="M386">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="387" spans="1:13">
+      <c r="A387" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B387" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E387" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="F387">
+        <v>11</v>
+      </c>
+      <c r="G387">
+        <v>14</v>
+      </c>
+      <c r="H387" t="s">
+        <v>39</v>
+      </c>
+      <c r="I387">
+        <v>0.87</v>
+      </c>
+      <c r="J387">
+        <v>1.02</v>
+      </c>
+      <c r="K387">
+        <v>2.5</v>
+      </c>
+      <c r="L387">
+        <v>1.06</v>
+      </c>
+      <c r="M387">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="388" spans="1:13">
+      <c r="A388" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B388" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D388" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E388" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F388">
+        <v>12</v>
+      </c>
+      <c r="G388">
+        <v>3</v>
+      </c>
+      <c r="H388" t="s">
+        <v>222</v>
+      </c>
+      <c r="I388">
+        <v>1.01</v>
+      </c>
+      <c r="J388">
+        <v>0.88</v>
+      </c>
+      <c r="K388" t="s">
+        <v>447</v>
+      </c>
+      <c r="L388">
+        <v>0.85</v>
+      </c>
+      <c r="M388">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13">
+      <c r="A389" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B389" s="5">
+        <v>0.0520833333333333</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D389" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E389" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F389">
+        <v>11</v>
+      </c>
+      <c r="G389">
+        <v>14</v>
+      </c>
+      <c r="H389" t="s">
+        <v>39</v>
+      </c>
+      <c r="I389">
+        <v>0.86</v>
+      </c>
+      <c r="J389">
+        <v>1.03</v>
+      </c>
+      <c r="K389" t="s">
+        <v>447</v>
+      </c>
+      <c r="L389">
+        <v>0.98</v>
+      </c>
+      <c r="M389">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="390" spans="1:13">
+      <c r="A390" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B390" s="5">
+        <v>0.229166666666667</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D390" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E390" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F390">
+        <v>13</v>
+      </c>
+      <c r="G390">
+        <v>10</v>
+      </c>
+      <c r="H390" t="s">
+        <v>164</v>
+      </c>
+      <c r="I390">
+        <v>1.02</v>
+      </c>
+      <c r="J390">
+        <v>0.87</v>
+      </c>
+      <c r="K390">
+        <v>2.5</v>
+      </c>
+      <c r="L390">
+        <v>1.05</v>
+      </c>
+      <c r="M390">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="391" spans="1:13">
+      <c r="A391" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B391" s="5">
+        <v>0.0520833333333333</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D391" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E391" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="F391">
+        <v>12</v>
+      </c>
+      <c r="G391">
+        <v>5</v>
+      </c>
+      <c r="H391" t="s">
+        <v>164</v>
+      </c>
+      <c r="I391">
+        <v>1.03</v>
+      </c>
+      <c r="J391">
+        <v>0.86</v>
+      </c>
+      <c r="K391" t="s">
+        <v>447</v>
+      </c>
+      <c r="L391">
+        <v>0.89</v>
+      </c>
+      <c r="M391">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="392" spans="1:13">
+      <c r="A392" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B392" s="5">
+        <v>0.9375</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D392" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E392" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F392">
+        <v>8</v>
+      </c>
+      <c r="G392">
+        <v>9</v>
+      </c>
+      <c r="H392" t="s">
+        <v>164</v>
+      </c>
+      <c r="I392">
+        <v>1.06</v>
+      </c>
+      <c r="J392">
+        <v>0.83</v>
+      </c>
+      <c r="K392" t="s">
+        <v>447</v>
+      </c>
+      <c r="L392">
+        <v>0.85</v>
+      </c>
+      <c r="M392">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="393" spans="1:13">
+      <c r="A393" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B393" s="5">
+        <v>0.916666666666667</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D393" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E393" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F393">
+        <v>5</v>
+      </c>
+      <c r="G393">
+        <v>2</v>
+      </c>
+      <c r="H393" t="s">
+        <v>164</v>
+      </c>
+      <c r="I393">
+        <v>0.86</v>
+      </c>
+      <c r="J393">
+        <v>1.03</v>
+      </c>
+      <c r="K393" t="s">
+        <v>443</v>
+      </c>
+      <c r="L393">
+        <v>0.97</v>
+      </c>
+      <c r="M393">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:13">
+      <c r="A394" s="3">
+        <v>46250</v>
+      </c>
+      <c r="B394" s="5">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D394" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E394" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F394">
+        <v>7</v>
+      </c>
+      <c r="G394">
+        <v>9</v>
+      </c>
+      <c r="H394" t="s">
+        <v>34</v>
+      </c>
+      <c r="I394">
+        <v>0.93</v>
+      </c>
+      <c r="J394">
+        <v>0.96</v>
+      </c>
+      <c r="K394" t="s">
+        <v>448</v>
+      </c>
+      <c r="L394">
+        <v>0.94</v>
+      </c>
+      <c r="M394">
+        <v>0.94</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E357" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E357">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E367" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:E367">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -10244,7 +11375,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -10553,7 +11684,7 @@
         <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>460</v>
+        <v>468</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -10570,7 +11701,7 @@
         <v>418</v>
       </c>
       <c r="E19" t="s">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -10587,7 +11718,7 @@
         <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>462</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -10604,7 +11735,7 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -10621,7 +11752,7 @@
         <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -10638,7 +11769,7 @@
         <v>421</v>
       </c>
       <c r="E23" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -10655,7 +11786,7 @@
         <v>427</v>
       </c>
       <c r="E24" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -10672,7 +11803,7 @@
         <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -10689,7 +11820,7 @@
         <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -10860,6 +11991,465 @@
       </c>
       <c r="E36" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B37" t="s">
+        <v>351</v>
+      </c>
+      <c r="C37" t="s">
+        <v>416</v>
+      </c>
+      <c r="D37" t="s">
+        <v>460</v>
+      </c>
+      <c r="E37" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B38" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" t="s">
+        <v>418</v>
+      </c>
+      <c r="E38" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B40" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" t="s">
+        <v>461</v>
+      </c>
+      <c r="D40" t="s">
+        <v>450</v>
+      </c>
+      <c r="E40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C41" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" t="s">
+        <v>81</v>
+      </c>
+      <c r="E41" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
+        <v>46248</v>
+      </c>
+      <c r="B42" t="s">
+        <v>309</v>
+      </c>
+      <c r="C42" t="s">
+        <v>394</v>
+      </c>
+      <c r="D42" t="s">
+        <v>361</v>
+      </c>
+      <c r="E42" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B43" t="s">
+        <v>351</v>
+      </c>
+      <c r="C43" t="s">
+        <v>353</v>
+      </c>
+      <c r="D43" t="s">
+        <v>371</v>
+      </c>
+      <c r="E43" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B44" t="s">
+        <v>351</v>
+      </c>
+      <c r="C44" t="s">
+        <v>368</v>
+      </c>
+      <c r="D44" t="s">
+        <v>462</v>
+      </c>
+      <c r="E44" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B45" t="s">
+        <v>351</v>
+      </c>
+      <c r="C45" t="s">
+        <v>374</v>
+      </c>
+      <c r="D45" t="s">
+        <v>370</v>
+      </c>
+      <c r="E45" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B46" t="s">
+        <v>351</v>
+      </c>
+      <c r="C46" t="s">
+        <v>355</v>
+      </c>
+      <c r="D46" t="s">
+        <v>373</v>
+      </c>
+      <c r="E46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47" t="s">
+        <v>49</v>
+      </c>
+      <c r="D47" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B48" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B49" t="s">
+        <v>309</v>
+      </c>
+      <c r="C49" t="s">
+        <v>463</v>
+      </c>
+      <c r="D49" t="s">
+        <v>363</v>
+      </c>
+      <c r="E49" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B50" t="s">
+        <v>309</v>
+      </c>
+      <c r="C50" t="s">
+        <v>464</v>
+      </c>
+      <c r="D50" t="s">
+        <v>310</v>
+      </c>
+      <c r="E50" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B51" t="s">
+        <v>422</v>
+      </c>
+      <c r="C51" t="s">
+        <v>465</v>
+      </c>
+      <c r="D51" t="s">
+        <v>430</v>
+      </c>
+      <c r="E51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" t="s">
+        <v>75</v>
+      </c>
+      <c r="D52" t="s">
+        <v>111</v>
+      </c>
+      <c r="E52" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
+        <v>46249</v>
+      </c>
+      <c r="B53" t="s">
+        <v>309</v>
+      </c>
+      <c r="C53" t="s">
+        <v>311</v>
+      </c>
+      <c r="D53" t="s">
+        <v>428</v>
+      </c>
+      <c r="E53" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B54" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" t="s">
+        <v>70</v>
+      </c>
+      <c r="D54" t="s">
+        <v>109</v>
+      </c>
+      <c r="E54" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B55" t="s">
+        <v>422</v>
+      </c>
+      <c r="C55" t="s">
+        <v>424</v>
+      </c>
+      <c r="D55" t="s">
+        <v>431</v>
+      </c>
+      <c r="E55" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B56" t="s">
+        <v>422</v>
+      </c>
+      <c r="C56" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" t="s">
+        <v>466</v>
+      </c>
+      <c r="E56" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+      <c r="C57" t="s">
+        <v>80</v>
+      </c>
+      <c r="D57" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B58" t="s">
+        <v>83</v>
+      </c>
+      <c r="C58" t="s">
+        <v>100</v>
+      </c>
+      <c r="D58" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B59" t="s">
+        <v>422</v>
+      </c>
+      <c r="C59" t="s">
+        <v>169</v>
+      </c>
+      <c r="D59" t="s">
+        <v>459</v>
+      </c>
+      <c r="E59" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B60" t="s">
+        <v>309</v>
+      </c>
+      <c r="C60" t="s">
+        <v>362</v>
+      </c>
+      <c r="D60" t="s">
+        <v>467</v>
+      </c>
+      <c r="E60" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B61" t="s">
+        <v>76</v>
+      </c>
+      <c r="C61" t="s">
+        <v>105</v>
+      </c>
+      <c r="D61" t="s">
+        <v>77</v>
+      </c>
+      <c r="E61" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B62" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" t="s">
+        <v>107</v>
+      </c>
+      <c r="D62" t="s">
+        <v>151</v>
+      </c>
+      <c r="E62" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B63" t="s">
+        <v>83</v>
+      </c>
+      <c r="C63" t="s">
+        <v>86</v>
+      </c>
+      <c r="D63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/复盘专用.xlsx
+++ b/复盘专用.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$367</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$394</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="486">
   <si>
     <t>旧数据</t>
   </si>
@@ -1435,6 +1435,33 @@
   </si>
   <si>
     <t>沙勒罗瓦</t>
+  </si>
+  <si>
+    <t>里奥夸尔托学院</t>
+  </si>
+  <si>
+    <t>1.5/2</t>
+  </si>
+  <si>
+    <t>防卫者</t>
+  </si>
+  <si>
+    <t>瑞模贝雷</t>
+  </si>
+  <si>
+    <t>甘拿斯亚门多萨</t>
+  </si>
+  <si>
+    <t>塔勒瑞斯</t>
+  </si>
+  <si>
+    <t>西甲</t>
+  </si>
+  <si>
+    <t>拉科鲁尼亚</t>
+  </si>
+  <si>
+    <t>埃尔切</t>
   </si>
   <si>
     <t>东京绿茵 +0/0.5</t>
@@ -2633,7 +2660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N394"/>
+  <dimension ref="A1:N402"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="2"/>
@@ -11360,9 +11387,337 @@
         <v>0.94</v>
       </c>
     </row>
+    <row r="395" spans="1:13">
+      <c r="A395" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B395" s="5">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="C395" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D395" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E395" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F395">
+        <v>6</v>
+      </c>
+      <c r="G395">
+        <v>9</v>
+      </c>
+      <c r="H395" t="s">
+        <v>161</v>
+      </c>
+      <c r="I395">
+        <v>1.04</v>
+      </c>
+      <c r="J395">
+        <v>0.85</v>
+      </c>
+      <c r="K395">
+        <v>3</v>
+      </c>
+      <c r="L395">
+        <v>0.94</v>
+      </c>
+      <c r="M395">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13">
+      <c r="A396" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B396" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C396" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D396" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E396" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F396">
+        <v>7</v>
+      </c>
+      <c r="G396">
+        <v>16</v>
+      </c>
+      <c r="H396" t="s">
+        <v>9</v>
+      </c>
+      <c r="I396">
+        <v>0.99</v>
+      </c>
+      <c r="J396">
+        <v>0.9</v>
+      </c>
+      <c r="K396" t="s">
+        <v>448</v>
+      </c>
+      <c r="L396">
+        <v>0.86</v>
+      </c>
+      <c r="M396">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="397" spans="1:13">
+      <c r="A397" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B397" s="5">
+        <v>0.0729166666666667</v>
+      </c>
+      <c r="C397" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D397" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E397" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F397">
+        <v>27</v>
+      </c>
+      <c r="G397">
+        <v>23</v>
+      </c>
+      <c r="H397" t="s">
+        <v>164</v>
+      </c>
+      <c r="I397">
+        <v>0.82</v>
+      </c>
+      <c r="J397">
+        <v>1.07</v>
+      </c>
+      <c r="K397" t="s">
+        <v>469</v>
+      </c>
+      <c r="L397">
+        <v>0.9</v>
+      </c>
+      <c r="M397">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="398" spans="1:13">
+      <c r="A398" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B398" s="5">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="C398" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D398" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E398" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="F398">
+        <v>16</v>
+      </c>
+      <c r="G398">
+        <v>18</v>
+      </c>
+      <c r="H398" t="s">
+        <v>161</v>
+      </c>
+      <c r="I398">
+        <v>1.05</v>
+      </c>
+      <c r="J398">
+        <v>0.84</v>
+      </c>
+      <c r="K398" t="s">
+        <v>469</v>
+      </c>
+      <c r="L398">
+        <v>0.8</v>
+      </c>
+      <c r="M398">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="399" spans="1:13">
+      <c r="A399" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B399" s="5">
+        <v>0.260416666666667</v>
+      </c>
+      <c r="C399" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D399" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E399" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F399">
+        <v>3</v>
+      </c>
+      <c r="G399">
+        <v>12</v>
+      </c>
+      <c r="H399" t="s">
+        <v>39</v>
+      </c>
+      <c r="I399">
+        <v>0.83</v>
+      </c>
+      <c r="J399">
+        <v>1.06</v>
+      </c>
+      <c r="K399" t="s">
+        <v>443</v>
+      </c>
+      <c r="L399">
+        <v>1.04</v>
+      </c>
+      <c r="M399">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="400" spans="1:13">
+      <c r="A400" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B400" s="5">
+        <v>0.291666666666667</v>
+      </c>
+      <c r="C400" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D400" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E400" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F400">
+        <v>17</v>
+      </c>
+      <c r="G400">
+        <v>18</v>
+      </c>
+      <c r="H400" t="s">
+        <v>34</v>
+      </c>
+      <c r="I400">
+        <v>0.9</v>
+      </c>
+      <c r="J400">
+        <v>0.99</v>
+      </c>
+      <c r="K400">
+        <v>2.5</v>
+      </c>
+      <c r="L400">
+        <v>0.83</v>
+      </c>
+      <c r="M400">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13">
+      <c r="A401" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B401" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C401" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D401" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E401" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="F401">
+        <v>19</v>
+      </c>
+      <c r="G401">
+        <v>28</v>
+      </c>
+      <c r="H401" t="s">
+        <v>65</v>
+      </c>
+      <c r="I401">
+        <v>1.16</v>
+      </c>
+      <c r="J401">
+        <v>0.75</v>
+      </c>
+      <c r="K401" t="s">
+        <v>469</v>
+      </c>
+      <c r="L401">
+        <v>0.81</v>
+      </c>
+      <c r="M401">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13">
+      <c r="A402" s="3">
+        <v>46251</v>
+      </c>
+      <c r="B402" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C402" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D402" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E402" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="F402">
+        <v>2</v>
+      </c>
+      <c r="G402">
+        <v>15</v>
+      </c>
+      <c r="H402" t="s">
+        <v>161</v>
+      </c>
+      <c r="I402">
+        <v>0.85</v>
+      </c>
+      <c r="J402">
+        <v>1.04</v>
+      </c>
+      <c r="K402" t="s">
+        <v>443</v>
+      </c>
+      <c r="L402">
+        <v>1.06</v>
+      </c>
+      <c r="M402">
+        <v>0.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E367" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E367">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E394" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:E394">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -11375,7 +11730,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -11684,7 +12039,7 @@
         <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -11701,7 +12056,7 @@
         <v>418</v>
       </c>
       <c r="E19" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -11718,7 +12073,7 @@
         <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -11735,7 +12090,7 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -11752,7 +12107,7 @@
         <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -11769,7 +12124,7 @@
         <v>421</v>
       </c>
       <c r="E23" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -11786,7 +12141,7 @@
         <v>427</v>
       </c>
       <c r="E24" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -11803,7 +12158,7 @@
         <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -11820,7 +12175,7 @@
         <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -12450,6 +12805,142 @@
       </c>
       <c r="E63" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B64" t="s">
+        <v>69</v>
+      </c>
+      <c r="C64" t="s">
+        <v>74</v>
+      </c>
+      <c r="D64" t="s">
+        <v>152</v>
+      </c>
+      <c r="E64" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B65" t="s">
+        <v>76</v>
+      </c>
+      <c r="C65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D65" t="s">
+        <v>96</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B66" t="s">
+        <v>170</v>
+      </c>
+      <c r="C66" t="s">
+        <v>468</v>
+      </c>
+      <c r="D66" t="s">
+        <v>172</v>
+      </c>
+      <c r="E66" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B67" t="s">
+        <v>170</v>
+      </c>
+      <c r="C67" t="s">
+        <v>265</v>
+      </c>
+      <c r="D67" t="s">
+        <v>414</v>
+      </c>
+      <c r="E67" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B68" t="s">
+        <v>170</v>
+      </c>
+      <c r="C68" t="s">
+        <v>413</v>
+      </c>
+      <c r="D68" t="s">
+        <v>470</v>
+      </c>
+      <c r="E68" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B69" t="s">
+        <v>422</v>
+      </c>
+      <c r="C69" t="s">
+        <v>267</v>
+      </c>
+      <c r="D69" t="s">
+        <v>471</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B70" t="s">
+        <v>170</v>
+      </c>
+      <c r="C70" t="s">
+        <v>472</v>
+      </c>
+      <c r="D70" t="s">
+        <v>473</v>
+      </c>
+      <c r="E70" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B71" t="s">
+        <v>474</v>
+      </c>
+      <c r="C71" t="s">
+        <v>475</v>
+      </c>
+      <c r="D71" t="s">
+        <v>476</v>
+      </c>
+      <c r="E71" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/复盘专用.xlsx
+++ b/复盘专用.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$402</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="501">
   <si>
     <t>旧数据</t>
   </si>
@@ -1462,6 +1462,51 @@
   </si>
   <si>
     <t>埃尔切</t>
+  </si>
+  <si>
+    <t>AEK雅典</t>
+  </si>
+  <si>
+    <t>解放者杯</t>
+  </si>
+  <si>
+    <t>托利马体育</t>
+  </si>
+  <si>
+    <t>山谷独立</t>
+  </si>
+  <si>
+    <t>智利天主大学</t>
+  </si>
+  <si>
+    <t>拉普拉塔大学生</t>
+  </si>
+  <si>
+    <t>圣保罗</t>
+  </si>
+  <si>
+    <t>玻利瓦尔</t>
+  </si>
+  <si>
+    <t>凯尔特人</t>
+  </si>
+  <si>
+    <t>LASK林茨</t>
+  </si>
+  <si>
+    <t>唐津市民</t>
+  </si>
+  <si>
+    <t>晋州市民</t>
+  </si>
+  <si>
+    <t>客让0</t>
+  </si>
+  <si>
+    <t>主让0</t>
+  </si>
+  <si>
+    <t>城南FC</t>
   </si>
   <si>
     <t>东京绿茵 +0/0.5</t>
@@ -2660,7 +2705,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N402"/>
+  <dimension ref="A1:N419"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="2"/>
@@ -11715,9 +11760,706 @@
         <v>0.83</v>
       </c>
     </row>
+    <row r="403" spans="1:13">
+      <c r="A403" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B403" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C403" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D403" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E403" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F403">
+        <v>3</v>
+      </c>
+      <c r="G403">
+        <v>2</v>
+      </c>
+      <c r="H403" t="s">
+        <v>166</v>
+      </c>
+      <c r="I403">
+        <v>0.87</v>
+      </c>
+      <c r="J403">
+        <v>1.02</v>
+      </c>
+      <c r="K403">
+        <v>3</v>
+      </c>
+      <c r="L403">
+        <v>0.85</v>
+      </c>
+      <c r="M403">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13">
+      <c r="A404" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B404" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C404" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D404" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E404" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F404">
+        <v>14</v>
+      </c>
+      <c r="G404">
+        <v>3</v>
+      </c>
+      <c r="H404" t="s">
+        <v>39</v>
+      </c>
+      <c r="I404">
+        <v>1.01</v>
+      </c>
+      <c r="J404">
+        <v>0.88</v>
+      </c>
+      <c r="K404">
+        <v>2.5</v>
+      </c>
+      <c r="L404">
+        <v>0.86</v>
+      </c>
+      <c r="M404">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13">
+      <c r="A405" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B405" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C405" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D405" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E405" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F405">
+        <v>4</v>
+      </c>
+      <c r="G405">
+        <v>1</v>
+      </c>
+      <c r="H405" t="s">
+        <v>164</v>
+      </c>
+      <c r="I405">
+        <v>0.92</v>
+      </c>
+      <c r="J405">
+        <v>0.97</v>
+      </c>
+      <c r="K405" t="s">
+        <v>443</v>
+      </c>
+      <c r="L405">
+        <v>1.13</v>
+      </c>
+      <c r="M405">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13">
+      <c r="A406" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B406" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C406" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D406" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E406" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="F406">
+        <v>3</v>
+      </c>
+      <c r="G406">
+        <v>1</v>
+      </c>
+      <c r="H406" t="s">
+        <v>65</v>
+      </c>
+      <c r="I406">
+        <v>0.8</v>
+      </c>
+      <c r="J406">
+        <v>1.09</v>
+      </c>
+      <c r="K406">
+        <v>2</v>
+      </c>
+      <c r="L406">
+        <v>0.88</v>
+      </c>
+      <c r="M406">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13">
+      <c r="A407" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B407" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C407" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E407" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F407">
+        <v>3</v>
+      </c>
+      <c r="G407">
+        <v>18</v>
+      </c>
+      <c r="H407" t="s">
+        <v>164</v>
+      </c>
+      <c r="I407">
+        <v>0.82</v>
+      </c>
+      <c r="J407">
+        <v>1.07</v>
+      </c>
+      <c r="K407">
+        <v>2</v>
+      </c>
+      <c r="L407">
+        <v>0.97</v>
+      </c>
+      <c r="M407">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13">
+      <c r="A408" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B408" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C408" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D408" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E408" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F408">
+        <v>13</v>
+      </c>
+      <c r="G408">
+        <v>2</v>
+      </c>
+      <c r="H408" t="s">
+        <v>190</v>
+      </c>
+      <c r="I408">
+        <v>0.99</v>
+      </c>
+      <c r="J408">
+        <v>0.9</v>
+      </c>
+      <c r="K408">
+        <v>2.5</v>
+      </c>
+      <c r="L408">
+        <v>0.85</v>
+      </c>
+      <c r="M408">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13">
+      <c r="A409" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B409" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C409" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D409" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E409" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F409">
+        <v>1</v>
+      </c>
+      <c r="G409">
+        <v>2</v>
+      </c>
+      <c r="H409" t="s">
+        <v>166</v>
+      </c>
+      <c r="I409">
+        <v>0.94</v>
+      </c>
+      <c r="J409">
+        <v>0.95</v>
+      </c>
+      <c r="K409" t="s">
+        <v>447</v>
+      </c>
+      <c r="L409">
+        <v>0.83</v>
+      </c>
+      <c r="M409">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13">
+      <c r="A410" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B410" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C410" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D410" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E410" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F410">
+        <v>10</v>
+      </c>
+      <c r="G410">
+        <v>1</v>
+      </c>
+      <c r="H410" t="s">
+        <v>164</v>
+      </c>
+      <c r="I410">
+        <v>0.82</v>
+      </c>
+      <c r="J410">
+        <v>1.07</v>
+      </c>
+      <c r="K410" t="s">
+        <v>448</v>
+      </c>
+      <c r="L410">
+        <v>0.91</v>
+      </c>
+      <c r="M410">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13">
+      <c r="A411" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B411" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C411" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D411" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E411" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F411">
+        <v>2</v>
+      </c>
+      <c r="G411">
+        <v>2</v>
+      </c>
+      <c r="H411" t="s">
+        <v>39</v>
+      </c>
+      <c r="I411">
+        <v>0.95</v>
+      </c>
+      <c r="J411">
+        <v>0.94</v>
+      </c>
+      <c r="K411">
+        <v>2.5</v>
+      </c>
+      <c r="L411">
+        <v>0.83</v>
+      </c>
+      <c r="M411">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13">
+      <c r="A412" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B412" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C412" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D412" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E412" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F412">
+        <v>1</v>
+      </c>
+      <c r="G412">
+        <v>4</v>
+      </c>
+      <c r="H412" t="s">
+        <v>164</v>
+      </c>
+      <c r="I412">
+        <v>1.05</v>
+      </c>
+      <c r="J412">
+        <v>0.84</v>
+      </c>
+      <c r="K412">
+        <v>2.5</v>
+      </c>
+      <c r="L412">
+        <v>0.82</v>
+      </c>
+      <c r="M412">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13">
+      <c r="A413" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B413" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C413" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D413" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E413" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F413">
+        <v>4</v>
+      </c>
+      <c r="G413">
+        <v>5</v>
+      </c>
+      <c r="H413" t="s">
+        <v>9</v>
+      </c>
+      <c r="I413">
+        <v>0.78</v>
+      </c>
+      <c r="J413">
+        <v>1.04</v>
+      </c>
+      <c r="K413">
+        <v>3</v>
+      </c>
+      <c r="L413">
+        <v>0.91</v>
+      </c>
+      <c r="M413">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13">
+      <c r="A414" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B414" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C414" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D414" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E414" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F414">
+        <v>7</v>
+      </c>
+      <c r="G414">
+        <v>11</v>
+      </c>
+      <c r="H414" t="s">
+        <v>164</v>
+      </c>
+      <c r="I414">
+        <v>0.94</v>
+      </c>
+      <c r="J414">
+        <v>0.88</v>
+      </c>
+      <c r="K414">
+        <v>2.5</v>
+      </c>
+      <c r="L414">
+        <v>0.95</v>
+      </c>
+      <c r="M414">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13">
+      <c r="A415" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B415" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C415" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D415" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E415" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F415">
+        <v>6</v>
+      </c>
+      <c r="G415">
+        <v>1</v>
+      </c>
+      <c r="H415" t="s">
+        <v>199</v>
+      </c>
+      <c r="I415">
+        <v>1.02</v>
+      </c>
+      <c r="J415">
+        <v>0.8</v>
+      </c>
+      <c r="K415">
+        <v>3</v>
+      </c>
+      <c r="L415">
+        <v>0.98</v>
+      </c>
+      <c r="M415">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13">
+      <c r="A416" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B416" s="5">
+        <v>0.75</v>
+      </c>
+      <c r="C416" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D416" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E416" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F416">
+        <v>11</v>
+      </c>
+      <c r="G416">
+        <v>12</v>
+      </c>
+      <c r="H416" t="s">
+        <v>40</v>
+      </c>
+      <c r="I416">
+        <v>0.93</v>
+      </c>
+      <c r="J416">
+        <v>0.89</v>
+      </c>
+      <c r="K416">
+        <v>2.5</v>
+      </c>
+      <c r="L416">
+        <v>1</v>
+      </c>
+      <c r="M416">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13">
+      <c r="A417" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B417" s="5">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="C417" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D417" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E417" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F417">
+        <v>7</v>
+      </c>
+      <c r="G417">
+        <v>5</v>
+      </c>
+      <c r="H417" t="s">
+        <v>489</v>
+      </c>
+      <c r="I417">
+        <v>1.03</v>
+      </c>
+      <c r="J417">
+        <v>0.79</v>
+      </c>
+      <c r="K417">
+        <v>2.5</v>
+      </c>
+      <c r="L417">
+        <v>0.82</v>
+      </c>
+      <c r="M417">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13">
+      <c r="A418" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B418" s="5">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="C418" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D418" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E418" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F418">
+        <v>5</v>
+      </c>
+      <c r="G418">
+        <v>9</v>
+      </c>
+      <c r="H418" t="s">
+        <v>490</v>
+      </c>
+      <c r="I418">
+        <v>0.78</v>
+      </c>
+      <c r="J418">
+        <v>1.04</v>
+      </c>
+      <c r="K418">
+        <v>2.5</v>
+      </c>
+      <c r="L418">
+        <v>0.85</v>
+      </c>
+      <c r="M418">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="419" spans="1:13">
+      <c r="A419" s="3">
+        <v>46253</v>
+      </c>
+      <c r="B419" s="5">
+        <v>0.770833333333333</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D419" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E419" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F419">
+        <v>3</v>
+      </c>
+      <c r="G419">
+        <v>11</v>
+      </c>
+      <c r="H419" t="s">
+        <v>166</v>
+      </c>
+      <c r="I419">
+        <v>1</v>
+      </c>
+      <c r="J419">
+        <v>0.82</v>
+      </c>
+      <c r="K419">
+        <v>2.5</v>
+      </c>
+      <c r="L419">
+        <v>0.88</v>
+      </c>
+      <c r="M419">
+        <v>0.92</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E394" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E394">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E402" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:E402">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -11730,7 +12472,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -12039,7 +12781,7 @@
         <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>477</v>
+        <v>492</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -12056,7 +12798,7 @@
         <v>418</v>
       </c>
       <c r="E19" t="s">
-        <v>478</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -12073,7 +12815,7 @@
         <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>479</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -12090,7 +12832,7 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>480</v>
+        <v>495</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -12107,7 +12849,7 @@
         <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>481</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -12124,7 +12866,7 @@
         <v>421</v>
       </c>
       <c r="E23" t="s">
-        <v>482</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -12141,7 +12883,7 @@
         <v>427</v>
       </c>
       <c r="E24" t="s">
-        <v>483</v>
+        <v>498</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -12158,7 +12900,7 @@
         <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>484</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -12175,7 +12917,7 @@
         <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>485</v>
+        <v>500</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -12941,6 +13683,295 @@
       </c>
       <c r="E71" t="s">
         <v>161</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B72" t="s">
+        <v>158</v>
+      </c>
+      <c r="C72" t="s">
+        <v>120</v>
+      </c>
+      <c r="D72" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B73" t="s">
+        <v>158</v>
+      </c>
+      <c r="C73" t="s">
+        <v>137</v>
+      </c>
+      <c r="D73" t="s">
+        <v>163</v>
+      </c>
+      <c r="E73" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B74" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" t="s">
+        <v>186</v>
+      </c>
+      <c r="D74" t="s">
+        <v>477</v>
+      </c>
+      <c r="E74" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B75" t="s">
+        <v>478</v>
+      </c>
+      <c r="C75" t="s">
+        <v>479</v>
+      </c>
+      <c r="D75" t="s">
+        <v>480</v>
+      </c>
+      <c r="E75" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B76" t="s">
+        <v>478</v>
+      </c>
+      <c r="C76" t="s">
+        <v>481</v>
+      </c>
+      <c r="D76" t="s">
+        <v>482</v>
+      </c>
+      <c r="E76" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="1">
+        <v>46252</v>
+      </c>
+      <c r="B77" t="s">
+        <v>456</v>
+      </c>
+      <c r="C77" t="s">
+        <v>483</v>
+      </c>
+      <c r="D77" t="s">
+        <v>484</v>
+      </c>
+      <c r="E77" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B78" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" t="s">
+        <v>485</v>
+      </c>
+      <c r="D78" t="s">
+        <v>486</v>
+      </c>
+      <c r="E78" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B79" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" t="s">
+        <v>189</v>
+      </c>
+      <c r="D79" t="s">
+        <v>85</v>
+      </c>
+      <c r="E79" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B80" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B81" t="s">
+        <v>158</v>
+      </c>
+      <c r="C81" t="s">
+        <v>184</v>
+      </c>
+      <c r="D81" t="s">
+        <v>125</v>
+      </c>
+      <c r="E81" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B82" t="s">
+        <v>127</v>
+      </c>
+      <c r="C82" t="s">
+        <v>103</v>
+      </c>
+      <c r="D82" t="s">
+        <v>487</v>
+      </c>
+      <c r="E82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B83" t="s">
+        <v>127</v>
+      </c>
+      <c r="C83" t="s">
+        <v>128</v>
+      </c>
+      <c r="D83" t="s">
+        <v>51</v>
+      </c>
+      <c r="E83" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B84" t="s">
+        <v>127</v>
+      </c>
+      <c r="C84" t="s">
+        <v>102</v>
+      </c>
+      <c r="D84" t="s">
+        <v>488</v>
+      </c>
+      <c r="E84" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B85" t="s">
+        <v>127</v>
+      </c>
+      <c r="C85" t="s">
+        <v>129</v>
+      </c>
+      <c r="D85" t="s">
+        <v>54</v>
+      </c>
+      <c r="E85" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B86" t="s">
+        <v>127</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86" t="s">
+        <v>52</v>
+      </c>
+      <c r="E86" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B87" t="s">
+        <v>127</v>
+      </c>
+      <c r="C87" t="s">
+        <v>130</v>
+      </c>
+      <c r="D87" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="1">
+        <v>46253</v>
+      </c>
+      <c r="B88" t="s">
+        <v>127</v>
+      </c>
+      <c r="C88" t="s">
+        <v>68</v>
+      </c>
+      <c r="D88" t="s">
+        <v>491</v>
+      </c>
+      <c r="E88" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/复盘专用.xlsx
+++ b/复盘专用.xlsx
@@ -11,7 +11,7 @@
     <sheet name="精选场次" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$402</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">赛事!$A$2:$E$419</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2117" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2513" uniqueCount="562">
   <si>
     <t>旧数据</t>
   </si>
@@ -1359,30 +1359,18 @@
     <t>小球水位</t>
   </si>
   <si>
-    <t>数据来源</t>
-  </si>
-  <si>
     <t>2/2.5</t>
   </si>
   <si>
-    <t>8月7日对话</t>
-  </si>
-  <si>
     <t>3.5/4</t>
   </si>
   <si>
-    <t>8月8日对话</t>
-  </si>
-  <si>
     <t>2.5/3</t>
   </si>
   <si>
     <t>3/3.5</t>
   </si>
   <si>
-    <t>8月9日对话</t>
-  </si>
-  <si>
     <t>班菲尔德</t>
   </si>
   <si>
@@ -1509,6 +1497,180 @@
     <t>城南FC</t>
   </si>
   <si>
+    <t>林肯红魔(中)</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>芬甲</t>
+  </si>
+  <si>
+    <t>卡亚尼卡帕</t>
+  </si>
+  <si>
+    <t>吉普</t>
+  </si>
+  <si>
+    <t>特拉布宗体育</t>
+  </si>
+  <si>
+    <t>布莱顿</t>
+  </si>
+  <si>
+    <t>克拉斯维克</t>
+  </si>
+  <si>
+    <t>俄杯</t>
+  </si>
+  <si>
+    <t>加里宁格勒巴</t>
+  </si>
+  <si>
+    <t>马哈奇卡拉</t>
+  </si>
+  <si>
+    <t>贝尔格莱德红星</t>
+  </si>
+  <si>
+    <t>比尔森胜利</t>
+  </si>
+  <si>
+    <t>OFI克里特</t>
+  </si>
+  <si>
+    <t>德利塔(中)</t>
+  </si>
+  <si>
+    <t>摩纳哥</t>
+  </si>
+  <si>
+    <t>亚特兰大</t>
+  </si>
+  <si>
+    <t>弗赖堡</t>
+  </si>
+  <si>
+    <t>巴列卡诺</t>
+  </si>
+  <si>
+    <t>阿拉维斯</t>
+  </si>
+  <si>
+    <t>英甲</t>
+  </si>
+  <si>
+    <t>谢周三</t>
+  </si>
+  <si>
+    <t>布拉德福德</t>
+  </si>
+  <si>
+    <t>布拉加</t>
+  </si>
+  <si>
+    <t>地拉拿迪纳摩(中)</t>
+  </si>
+  <si>
+    <t>赫塔菲</t>
+  </si>
+  <si>
+    <t>马卡拉</t>
+  </si>
+  <si>
+    <t>桑托斯</t>
+  </si>
+  <si>
+    <t>亚松森奥林匹克</t>
+  </si>
+  <si>
+    <t>瓦斯科达伽马</t>
+  </si>
+  <si>
+    <t>巴西竞技</t>
+  </si>
+  <si>
+    <t>雷加塔斯巴西</t>
+  </si>
+  <si>
+    <t>诺瓦里桑蒂诺</t>
+  </si>
+  <si>
+    <t>米内罗美洲</t>
+  </si>
+  <si>
+    <t>美职业</t>
+  </si>
+  <si>
+    <t>堪萨斯城竞技</t>
+  </si>
+  <si>
+    <t>圣路易斯城</t>
+  </si>
+  <si>
+    <t>大小球2.5</t>
+  </si>
+  <si>
+    <t>图尔克</t>
+  </si>
+  <si>
+    <t>泰格雷</t>
+  </si>
+  <si>
+    <t>圣塔菲</t>
+  </si>
+  <si>
+    <t>河床</t>
+  </si>
+  <si>
+    <t>保地花高SP</t>
+  </si>
+  <si>
+    <t>克里丘马</t>
+  </si>
+  <si>
+    <t>明尼苏达联</t>
+  </si>
+  <si>
+    <t>亚特兰大联</t>
+  </si>
+  <si>
+    <t>科罗拉多急流</t>
+  </si>
+  <si>
+    <t>洛杉矶FC</t>
+  </si>
+  <si>
+    <t>皇家盐湖城</t>
+  </si>
+  <si>
+    <t>达拉斯FC</t>
+  </si>
+  <si>
+    <t>西雅图海湾人</t>
+  </si>
+  <si>
+    <t>奥斯汀FC</t>
+  </si>
+  <si>
+    <t>洛杉矶银河</t>
+  </si>
+  <si>
+    <t>圣何塞地震</t>
+  </si>
+  <si>
+    <t>波特兰伐木者</t>
+  </si>
+  <si>
+    <t>圣地亚哥</t>
+  </si>
+  <si>
+    <t>温哥华白浪</t>
+  </si>
+  <si>
+    <t>休斯敦迪纳摩</t>
+  </si>
+  <si>
     <t>东京绿茵 +0/0.5</t>
   </si>
   <si>
@@ -1534,6 +1696,27 @@
   </si>
   <si>
     <t>帕尔梅拉斯 -0.5/1</t>
+  </si>
+  <si>
+    <t>赫拉德茨</t>
+  </si>
+  <si>
+    <t>瑞典杯</t>
+  </si>
+  <si>
+    <t>派提亚</t>
+  </si>
+  <si>
+    <t>客让3</t>
+  </si>
+  <si>
+    <t>FC阿尔兰达</t>
+  </si>
+  <si>
+    <t>奥斯特桑斯</t>
+  </si>
+  <si>
+    <t>加里宁格勒</t>
   </si>
 </sst>
 </file>
@@ -2705,7 +2888,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N419"/>
+  <dimension ref="A1:M475"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="16" style="2"/>
@@ -7868,7 +8051,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="305" spans="1:14">
+    <row r="305" spans="1:13">
       <c r="A305" s="3">
         <v>46243.8541666667</v>
       </c>
@@ -7885,7 +8068,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="306" spans="1:14">
+    <row r="306" spans="1:13">
       <c r="A306" s="3">
         <v>46243.8541666667</v>
       </c>
@@ -7902,7 +8085,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="307" spans="1:14">
+    <row r="307" spans="1:13">
       <c r="A307" s="3">
         <v>46243.9166666667</v>
       </c>
@@ -7919,7 +8102,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="308" spans="1:14">
+    <row r="308" spans="1:13">
       <c r="A308" s="3">
         <v>46243.9166666667</v>
       </c>
@@ -7936,7 +8119,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="309" spans="1:14">
+    <row r="309" spans="1:13">
       <c r="A309" s="3">
         <v>46243.0208333333</v>
       </c>
@@ -7953,7 +8136,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="310" spans="1:14">
+    <row r="310" spans="1:13">
       <c r="A310" s="3">
         <v>46243.0520833333</v>
       </c>
@@ -7970,7 +8153,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="311" spans="1:14">
+    <row r="311" spans="1:13">
       <c r="A311" s="3">
         <v>46243.125</v>
       </c>
@@ -7987,7 +8170,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="312" spans="1:14">
+    <row r="312" spans="1:13">
       <c r="A312" s="3">
         <v>46243.2708333333</v>
       </c>
@@ -8004,12 +8187,12 @@
         <v>166</v>
       </c>
     </row>
-    <row r="313" spans="1:14">
+    <row r="313" spans="1:13">
       <c r="A313" s="2" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="314" spans="1:14">
+    <row r="314" spans="1:13">
       <c r="A314" s="2" t="s">
         <v>1</v>
       </c>
@@ -8049,11 +8232,8 @@
       <c r="M314" t="s">
         <v>441</v>
       </c>
-      <c r="N314" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="315" spans="1:14">
+    </row>
+    <row r="315" spans="1:13">
       <c r="A315" s="3">
         <v>46241</v>
       </c>
@@ -8085,7 +8265,7 @@
         <v>0.86</v>
       </c>
       <c r="K315" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L315">
         <v>0.99</v>
@@ -8093,11 +8273,8 @@
       <c r="M315">
         <v>0.89</v>
       </c>
-      <c r="N315" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="316" spans="1:14">
+    </row>
+    <row r="316" spans="1:13">
       <c r="A316" s="3">
         <v>46241</v>
       </c>
@@ -8137,11 +8314,8 @@
       <c r="M316">
         <v>1.01</v>
       </c>
-      <c r="N316" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="317" spans="1:14">
+    </row>
+    <row r="317" spans="1:13">
       <c r="A317" s="3">
         <v>46241</v>
       </c>
@@ -8181,11 +8355,8 @@
       <c r="M317">
         <v>0.99</v>
       </c>
-      <c r="N317" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="318" spans="1:14">
+    </row>
+    <row r="318" spans="1:13">
       <c r="A318" s="3">
         <v>46241</v>
       </c>
@@ -8217,7 +8388,7 @@
         <v>0.85</v>
       </c>
       <c r="K318" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L318">
         <v>0.8</v>
@@ -8225,11 +8396,8 @@
       <c r="M318">
         <v>1</v>
       </c>
-      <c r="N318" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="319" spans="1:14">
+    </row>
+    <row r="319" spans="1:13">
       <c r="A319" s="3">
         <v>46242</v>
       </c>
@@ -8269,11 +8437,8 @@
       <c r="M319">
         <v>0.9</v>
       </c>
-      <c r="N319" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="320" spans="1:14">
+    </row>
+    <row r="320" spans="1:13">
       <c r="A320" s="3">
         <v>46242</v>
       </c>
@@ -8313,11 +8478,8 @@
       <c r="M320">
         <v>0.88</v>
       </c>
-      <c r="N320" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="321" spans="1:14">
+    </row>
+    <row r="321" spans="1:13">
       <c r="A321" s="3">
         <v>46242</v>
       </c>
@@ -8357,11 +8519,8 @@
       <c r="M321">
         <v>0.94</v>
       </c>
-      <c r="N321" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="322" spans="1:14">
+    </row>
+    <row r="322" spans="1:13">
       <c r="A322" s="3">
         <v>46242</v>
       </c>
@@ -8401,11 +8560,8 @@
       <c r="M322">
         <v>0.95</v>
       </c>
-      <c r="N322" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="323" spans="1:14">
+    </row>
+    <row r="323" spans="1:13">
       <c r="A323" s="3">
         <v>46242</v>
       </c>
@@ -8437,7 +8593,7 @@
         <v>0.82</v>
       </c>
       <c r="K323" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L323">
         <v>1.07</v>
@@ -8445,11 +8601,8 @@
       <c r="M323">
         <v>0.81</v>
       </c>
-      <c r="N323" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="324" spans="1:14">
+    </row>
+    <row r="324" spans="1:13">
       <c r="A324" s="3">
         <v>46242</v>
       </c>
@@ -8489,11 +8642,8 @@
       <c r="M324">
         <v>0.9</v>
       </c>
-      <c r="N324" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="325" spans="1:14">
+    </row>
+    <row r="325" spans="1:13">
       <c r="A325" s="3">
         <v>46242</v>
       </c>
@@ -8533,11 +8683,8 @@
       <c r="M325">
         <v>1.04</v>
       </c>
-      <c r="N325" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="326" spans="1:14">
+    </row>
+    <row r="326" spans="1:13">
       <c r="A326" s="3">
         <v>46242</v>
       </c>
@@ -8577,11 +8724,8 @@
       <c r="M326">
         <v>0.83</v>
       </c>
-      <c r="N326" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="327" spans="1:14">
+    </row>
+    <row r="327" spans="1:13">
       <c r="A327" s="3">
         <v>46242</v>
       </c>
@@ -8613,7 +8757,7 @@
         <v>1.05</v>
       </c>
       <c r="K327" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L327">
         <v>0.87</v>
@@ -8621,11 +8765,8 @@
       <c r="M327">
         <v>1.01</v>
       </c>
-      <c r="N327" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="328" spans="1:14">
+    </row>
+    <row r="328" spans="1:13">
       <c r="A328" s="3">
         <v>46242</v>
       </c>
@@ -8657,7 +8798,7 @@
         <v>1.06</v>
       </c>
       <c r="K328" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L328">
         <v>0.9</v>
@@ -8665,11 +8806,8 @@
       <c r="M328">
         <v>0.98</v>
       </c>
-      <c r="N328" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="329" spans="1:14">
+    </row>
+    <row r="329" spans="1:13">
       <c r="A329" s="3">
         <v>46242</v>
       </c>
@@ -8709,11 +8847,8 @@
       <c r="M329">
         <v>0.92</v>
       </c>
-      <c r="N329" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="330" spans="1:14">
+    </row>
+    <row r="330" spans="1:13">
       <c r="A330" s="3">
         <v>46242</v>
       </c>
@@ -8753,11 +8888,8 @@
       <c r="M330">
         <v>1.03</v>
       </c>
-      <c r="N330" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="331" spans="1:14">
+    </row>
+    <row r="331" spans="1:13">
       <c r="A331" s="3">
         <v>46242</v>
       </c>
@@ -8797,11 +8929,8 @@
       <c r="M331">
         <v>0.85</v>
       </c>
-      <c r="N331" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="332" spans="1:14">
+    </row>
+    <row r="332" spans="1:13">
       <c r="A332" s="3">
         <v>46242</v>
       </c>
@@ -8833,7 +8962,7 @@
         <v>1.01</v>
       </c>
       <c r="K332" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L332">
         <v>1.05</v>
@@ -8841,11 +8970,8 @@
       <c r="M332">
         <v>0.82</v>
       </c>
-      <c r="N332" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="333" spans="1:14">
+    </row>
+    <row r="333" spans="1:13">
       <c r="A333" s="3">
         <v>46242</v>
       </c>
@@ -8877,7 +9003,7 @@
         <v>0.85</v>
       </c>
       <c r="K333" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L333">
         <v>0.9</v>
@@ -8885,11 +9011,8 @@
       <c r="M333">
         <v>0.9</v>
       </c>
-      <c r="N333" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="334" spans="1:14">
+    </row>
+    <row r="334" spans="1:13">
       <c r="A334" s="3">
         <v>46242</v>
       </c>
@@ -8921,7 +9044,7 @@
         <v>1.08</v>
       </c>
       <c r="K334" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L334">
         <v>0.87</v>
@@ -8929,11 +9052,8 @@
       <c r="M334">
         <v>1</v>
       </c>
-      <c r="N334" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="335" spans="1:14">
+    </row>
+    <row r="335" spans="1:13">
       <c r="A335" s="3">
         <v>46242</v>
       </c>
@@ -8973,11 +9093,8 @@
       <c r="M335">
         <v>0.83</v>
       </c>
-      <c r="N335" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="336" spans="1:14">
+    </row>
+    <row r="336" spans="1:13">
       <c r="A336" s="3">
         <v>46242</v>
       </c>
@@ -9009,7 +9126,7 @@
         <v>0.96</v>
       </c>
       <c r="K336" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L336">
         <v>0.99</v>
@@ -9017,11 +9134,8 @@
       <c r="M336">
         <v>0.88</v>
       </c>
-      <c r="N336" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="337" spans="1:14">
+    </row>
+    <row r="337" spans="1:13">
       <c r="A337" s="3">
         <v>46242</v>
       </c>
@@ -9061,11 +9175,8 @@
       <c r="M337">
         <v>0.85</v>
       </c>
-      <c r="N337" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="338" spans="1:14">
+    </row>
+    <row r="338" spans="1:13">
       <c r="A338" s="3">
         <v>46242</v>
       </c>
@@ -9105,11 +9216,8 @@
       <c r="M338">
         <v>0.93</v>
       </c>
-      <c r="N338" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="339" spans="1:14">
+    </row>
+    <row r="339" spans="1:13">
       <c r="A339" s="3">
         <v>46243</v>
       </c>
@@ -9141,7 +9249,7 @@
         <v>0.89</v>
       </c>
       <c r="K339" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L339">
         <v>0.94</v>
@@ -9149,11 +9257,8 @@
       <c r="M339">
         <v>0.92</v>
       </c>
-      <c r="N339" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="340" spans="1:14">
+    </row>
+    <row r="340" spans="1:13">
       <c r="A340" s="3">
         <v>46243</v>
       </c>
@@ -9193,11 +9298,8 @@
       <c r="M340">
         <v>0.87</v>
       </c>
-      <c r="N340" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="341" spans="1:14">
+    </row>
+    <row r="341" spans="1:13">
       <c r="A341" s="3">
         <v>46243</v>
       </c>
@@ -9237,11 +9339,8 @@
       <c r="M341">
         <v>0.89</v>
       </c>
-      <c r="N341" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="342" spans="1:14">
+    </row>
+    <row r="342" spans="1:13">
       <c r="A342" s="3">
         <v>46243</v>
       </c>
@@ -9273,7 +9372,7 @@
         <v>0.98</v>
       </c>
       <c r="K342" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L342">
         <v>0.89</v>
@@ -9281,11 +9380,8 @@
       <c r="M342">
         <v>0.98</v>
       </c>
-      <c r="N342" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="343" spans="1:14">
+    </row>
+    <row r="343" spans="1:13">
       <c r="A343" s="3">
         <v>46243</v>
       </c>
@@ -9317,7 +9413,7 @@
         <v>0.97</v>
       </c>
       <c r="K343" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L343">
         <v>1</v>
@@ -9325,11 +9421,8 @@
       <c r="M343">
         <v>0.86</v>
       </c>
-      <c r="N343" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="344" spans="1:14">
+    </row>
+    <row r="344" spans="1:13">
       <c r="A344" s="3">
         <v>46243</v>
       </c>
@@ -9361,7 +9454,7 @@
         <v>0.79</v>
       </c>
       <c r="K344" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L344">
         <v>0.88</v>
@@ -9369,11 +9462,8 @@
       <c r="M344">
         <v>1</v>
       </c>
-      <c r="N344" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="345" spans="1:14">
+    </row>
+    <row r="345" spans="1:13">
       <c r="A345" s="3">
         <v>46243</v>
       </c>
@@ -9413,11 +9503,8 @@
       <c r="M345">
         <v>0.92</v>
       </c>
-      <c r="N345" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="346" spans="1:14">
+    </row>
+    <row r="346" spans="1:13">
       <c r="A346" s="3">
         <v>46243</v>
       </c>
@@ -9449,7 +9536,7 @@
         <v>0.83</v>
       </c>
       <c r="K346" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L346">
         <v>0.83</v>
@@ -9457,11 +9544,8 @@
       <c r="M346">
         <v>1.04</v>
       </c>
-      <c r="N346" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="347" spans="1:14">
+    </row>
+    <row r="347" spans="1:13">
       <c r="A347" s="3">
         <v>46243</v>
       </c>
@@ -9501,11 +9585,8 @@
       <c r="M347">
         <v>0.9</v>
       </c>
-      <c r="N347" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="348" spans="1:14">
+    </row>
+    <row r="348" spans="1:13">
       <c r="A348" s="3">
         <v>46244</v>
       </c>
@@ -9537,7 +9618,7 @@
         <v>0.94</v>
       </c>
       <c r="K348" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L348">
         <v>0.91</v>
@@ -9546,7 +9627,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="349" spans="1:14">
+    <row r="349" spans="1:13">
       <c r="A349" s="3">
         <v>46244</v>
       </c>
@@ -9587,7 +9668,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="350" spans="1:14">
+    <row r="350" spans="1:13">
       <c r="A350" s="3">
         <v>46244</v>
       </c>
@@ -9598,10 +9679,10 @@
         <v>170</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="F350">
         <v>23</v>
@@ -9628,7 +9709,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="351" spans="1:14">
+    <row r="351" spans="1:13">
       <c r="A351" s="3">
         <v>46244</v>
       </c>
@@ -9642,7 +9723,7 @@
         <v>264</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F351">
         <v>15</v>
@@ -9660,7 +9741,7 @@
         <v>0.93</v>
       </c>
       <c r="K351" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L351">
         <v>0.88</v>
@@ -9669,7 +9750,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="352" spans="1:14">
+    <row r="352" spans="1:13">
       <c r="A352" s="3">
         <v>46245</v>
       </c>
@@ -9677,13 +9758,13 @@
         <v>0.729166666666667</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F352">
         <v>2</v>
@@ -9701,7 +9782,7 @@
         <v>0.8</v>
       </c>
       <c r="K352" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L352">
         <v>0.86</v>
@@ -9718,7 +9799,7 @@
         <v>0.770833333333333</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D353" s="2" t="s">
         <v>68</v>
@@ -9742,7 +9823,7 @@
         <v>0.82</v>
       </c>
       <c r="K353" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L353">
         <v>0.95</v>
@@ -9824,7 +9905,7 @@
         <v>0.89</v>
       </c>
       <c r="K355" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L355">
         <v>0.86</v>
@@ -9923,10 +10004,10 @@
         <v>0.25</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>195</v>
@@ -9947,7 +10028,7 @@
         <v>0.82</v>
       </c>
       <c r="K358" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L358">
         <v>0.84</v>
@@ -10070,7 +10151,7 @@
         <v>0.97</v>
       </c>
       <c r="K361" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L361">
         <v>0.99</v>
@@ -10087,13 +10168,13 @@
         <v>0.354166666666667</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F362">
         <v>16</v>
@@ -10193,7 +10274,7 @@
         <v>1.03</v>
       </c>
       <c r="K364" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L364">
         <v>0.92</v>
@@ -10275,7 +10356,7 @@
         <v>0.79</v>
       </c>
       <c r="K366" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L366">
         <v>0.99</v>
@@ -10316,7 +10397,7 @@
         <v>0.97</v>
       </c>
       <c r="K367" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L367">
         <v>0.79</v>
@@ -10339,7 +10420,7 @@
         <v>416</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F368">
         <v>10</v>
@@ -10357,7 +10438,7 @@
         <v>0.9</v>
       </c>
       <c r="K368" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L368">
         <v>1.06</v>
@@ -10398,7 +10479,7 @@
         <v>0.85</v>
       </c>
       <c r="K369" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L369">
         <v>1</v>
@@ -10439,7 +10520,7 @@
         <v>1.07</v>
       </c>
       <c r="K370" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L370">
         <v>0.86</v>
@@ -10480,7 +10561,7 @@
         <v>1.04</v>
       </c>
       <c r="K371" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L371">
         <v>0.91</v>
@@ -10521,7 +10602,7 @@
         <v>1.01</v>
       </c>
       <c r="K372" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L372">
         <v>0.95</v>
@@ -10541,10 +10622,10 @@
         <v>170</v>
       </c>
       <c r="D373" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="F373">
         <v>16</v>
@@ -10626,7 +10707,7 @@
         <v>368</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="F375">
         <v>16</v>
@@ -10644,7 +10725,7 @@
         <v>0.93</v>
       </c>
       <c r="K375" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L375">
         <v>0.85</v>
@@ -10685,7 +10766,7 @@
         <v>0.96</v>
       </c>
       <c r="K376" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L376">
         <v>0.98</v>
@@ -10808,7 +10889,7 @@
         <v>1.05</v>
       </c>
       <c r="K379" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L379">
         <v>0.81</v>
@@ -10828,7 +10909,7 @@
         <v>309</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>363</v>
@@ -10869,7 +10950,7 @@
         <v>309</v>
       </c>
       <c r="D381" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>310</v>
@@ -10890,7 +10971,7 @@
         <v>1.07</v>
       </c>
       <c r="K381" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L381">
         <v>0.98</v>
@@ -10910,7 +10991,7 @@
         <v>422</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>430</v>
@@ -10931,7 +11012,7 @@
         <v>0.8</v>
       </c>
       <c r="K382" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L382">
         <v>1.05</v>
@@ -10972,7 +11053,7 @@
         <v>1.09</v>
       </c>
       <c r="K383" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L383">
         <v>0.94</v>
@@ -11118,7 +11199,7 @@
         <v>195</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="F387">
         <v>11</v>
@@ -11177,7 +11258,7 @@
         <v>0.88</v>
       </c>
       <c r="K388" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L388">
         <v>0.85</v>
@@ -11218,7 +11299,7 @@
         <v>1.03</v>
       </c>
       <c r="K389" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L389">
         <v>0.98</v>
@@ -11241,7 +11322,7 @@
         <v>169</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="F390">
         <v>13</v>
@@ -11282,7 +11363,7 @@
         <v>362</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F391">
         <v>12</v>
@@ -11300,7 +11381,7 @@
         <v>0.86</v>
       </c>
       <c r="K391" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L391">
         <v>0.89</v>
@@ -11341,7 +11422,7 @@
         <v>0.83</v>
       </c>
       <c r="K392" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L392">
         <v>0.85</v>
@@ -11382,7 +11463,7 @@
         <v>1.03</v>
       </c>
       <c r="K393" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L393">
         <v>0.97</v>
@@ -11423,7 +11504,7 @@
         <v>0.96</v>
       </c>
       <c r="K394" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L394">
         <v>0.94</v>
@@ -11505,7 +11586,7 @@
         <v>0.9</v>
       </c>
       <c r="K396" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L396">
         <v>0.86</v>
@@ -11525,7 +11606,7 @@
         <v>170</v>
       </c>
       <c r="D397" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>172</v>
@@ -11546,7 +11627,7 @@
         <v>1.07</v>
       </c>
       <c r="K397" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="L397">
         <v>0.9</v>
@@ -11587,7 +11668,7 @@
         <v>0.84</v>
       </c>
       <c r="K398" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="L398">
         <v>0.8</v>
@@ -11610,7 +11691,7 @@
         <v>413</v>
       </c>
       <c r="E399" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="F399">
         <v>3</v>
@@ -11628,7 +11709,7 @@
         <v>1.06</v>
       </c>
       <c r="K399" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L399">
         <v>1.04</v>
@@ -11651,7 +11732,7 @@
         <v>267</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F400">
         <v>17</v>
@@ -11689,10 +11770,10 @@
         <v>170</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="F401">
         <v>19</v>
@@ -11710,7 +11791,7 @@
         <v>0.75</v>
       </c>
       <c r="K401" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="L401">
         <v>0.81</v>
@@ -11727,13 +11808,13 @@
         <v>0.125</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="F402">
         <v>2</v>
@@ -11751,7 +11832,7 @@
         <v>1.04</v>
       </c>
       <c r="K402" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L402">
         <v>1.06</v>
@@ -11856,7 +11937,7 @@
         <v>186</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F405">
         <v>4</v>
@@ -11874,7 +11955,7 @@
         <v>0.97</v>
       </c>
       <c r="K405" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L405">
         <v>1.13</v>
@@ -11891,13 +11972,13 @@
         <v>0.354166666666667</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F406">
         <v>3</v>
@@ -11932,13 +12013,13 @@
         <v>0.354166666666667</v>
       </c>
       <c r="C407" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D407" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E407" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="D407" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="E407" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="F407">
         <v>3</v>
@@ -11973,13 +12054,13 @@
         <v>0.354166666666667</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F408">
         <v>13</v>
@@ -12017,10 +12098,10 @@
         <v>158</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F409">
         <v>1</v>
@@ -12038,7 +12119,7 @@
         <v>0.95</v>
       </c>
       <c r="K409" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="L409">
         <v>0.83</v>
@@ -12079,7 +12160,7 @@
         <v>1.07</v>
       </c>
       <c r="K410" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="L410">
         <v>0.91</v>
@@ -12184,7 +12265,7 @@
         <v>103</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F413">
         <v>4</v>
@@ -12266,7 +12347,7 @@
         <v>102</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="F415">
         <v>6</v>
@@ -12357,7 +12438,7 @@
         <v>5</v>
       </c>
       <c r="H417" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="I417">
         <v>1.03</v>
@@ -12398,7 +12479,7 @@
         <v>9</v>
       </c>
       <c r="H418" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="I418">
         <v>0.78</v>
@@ -12430,7 +12511,7 @@
         <v>68</v>
       </c>
       <c r="E419" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F419">
         <v>3</v>
@@ -12457,9 +12538,2305 @@
         <v>0.92</v>
       </c>
     </row>
+    <row r="420" spans="1:13">
+      <c r="A420" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B420" s="5">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="C420" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D420" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E420" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F420">
+        <v>2</v>
+      </c>
+      <c r="G420">
+        <v>9</v>
+      </c>
+      <c r="H420" t="s">
+        <v>164</v>
+      </c>
+      <c r="I420">
+        <v>0.95</v>
+      </c>
+      <c r="J420">
+        <v>0.94</v>
+      </c>
+      <c r="K420" t="s">
+        <v>442</v>
+      </c>
+      <c r="L420">
+        <v>1.05</v>
+      </c>
+      <c r="M420">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="421" spans="1:13">
+      <c r="A421" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B421" s="5">
+        <v>0</v>
+      </c>
+      <c r="C421" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D421" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E421" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F421">
+        <v>7</v>
+      </c>
+      <c r="G421">
+        <v>3</v>
+      </c>
+      <c r="H421" t="s">
+        <v>190</v>
+      </c>
+      <c r="I421">
+        <v>0.86</v>
+      </c>
+      <c r="J421">
+        <v>1.03</v>
+      </c>
+      <c r="K421" t="s">
+        <v>444</v>
+      </c>
+      <c r="L421">
+        <v>0.97</v>
+      </c>
+      <c r="M421">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="422" spans="1:13">
+      <c r="A422" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B422" s="5">
+        <v>0</v>
+      </c>
+      <c r="C422" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D422" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E422" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F422">
+        <v>11</v>
+      </c>
+      <c r="G422">
+        <v>3</v>
+      </c>
+      <c r="H422" t="s">
+        <v>222</v>
+      </c>
+      <c r="I422">
+        <v>0.95</v>
+      </c>
+      <c r="J422">
+        <v>0.94</v>
+      </c>
+      <c r="K422">
+        <v>3</v>
+      </c>
+      <c r="L422">
+        <v>0.98</v>
+      </c>
+      <c r="M422">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="423" spans="1:13">
+      <c r="A423" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B423" s="5">
+        <v>0</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D423" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E423" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F423">
+        <v>2</v>
+      </c>
+      <c r="G423">
+        <v>2</v>
+      </c>
+      <c r="H423" t="s">
+        <v>26</v>
+      </c>
+      <c r="I423">
+        <v>1.03</v>
+      </c>
+      <c r="J423">
+        <v>0.79</v>
+      </c>
+      <c r="K423">
+        <v>3</v>
+      </c>
+      <c r="L423">
+        <v>1.04</v>
+      </c>
+      <c r="M423">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="424" spans="1:13">
+      <c r="A424" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B424" s="5">
+        <v>0</v>
+      </c>
+      <c r="C424" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D424" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E424" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F424" t="s">
+        <v>489</v>
+      </c>
+      <c r="G424">
+        <v>9</v>
+      </c>
+      <c r="H424" t="s">
+        <v>164</v>
+      </c>
+      <c r="I424">
+        <v>0.97</v>
+      </c>
+      <c r="J424">
+        <v>0.85</v>
+      </c>
+      <c r="K424" t="s">
+        <v>442</v>
+      </c>
+      <c r="L424">
+        <v>0.84</v>
+      </c>
+      <c r="M424">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="425" spans="1:13">
+      <c r="A425" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B425" s="5">
+        <v>0.958333333333333</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="D425" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E425" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F425">
+        <v>8</v>
+      </c>
+      <c r="G425">
+        <v>4</v>
+      </c>
+      <c r="H425" t="s">
+        <v>222</v>
+      </c>
+      <c r="I425">
+        <v>1.03</v>
+      </c>
+      <c r="J425">
+        <v>0.86</v>
+      </c>
+      <c r="K425" t="s">
+        <v>444</v>
+      </c>
+      <c r="L425">
+        <v>0.88</v>
+      </c>
+      <c r="M425">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="426" spans="1:13">
+      <c r="A426" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B426" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C426" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D426" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E426" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F426">
+        <v>4</v>
+      </c>
+      <c r="G426">
+        <v>2</v>
+      </c>
+      <c r="H426" t="s">
+        <v>403</v>
+      </c>
+      <c r="I426">
+        <v>0.85</v>
+      </c>
+      <c r="J426">
+        <v>1.04</v>
+      </c>
+      <c r="K426" t="s">
+        <v>445</v>
+      </c>
+      <c r="L426">
+        <v>0.91</v>
+      </c>
+      <c r="M426">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="427" spans="1:13">
+      <c r="A427" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B427" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C427" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D427" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E427" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F427">
+        <v>8</v>
+      </c>
+      <c r="G427">
+        <v>5</v>
+      </c>
+      <c r="H427" t="s">
+        <v>164</v>
+      </c>
+      <c r="I427">
+        <v>0.99</v>
+      </c>
+      <c r="J427">
+        <v>0.9</v>
+      </c>
+      <c r="K427">
+        <v>2.5</v>
+      </c>
+      <c r="L427">
+        <v>0.86</v>
+      </c>
+      <c r="M427">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="428" spans="1:13">
+      <c r="A428" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B428" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C428" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D428" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="E428" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F428">
+        <v>10</v>
+      </c>
+      <c r="G428">
+        <v>8</v>
+      </c>
+      <c r="H428" t="s">
+        <v>166</v>
+      </c>
+      <c r="I428">
+        <v>0.85</v>
+      </c>
+      <c r="J428">
+        <v>1.04</v>
+      </c>
+      <c r="K428" t="s">
+        <v>444</v>
+      </c>
+      <c r="L428">
+        <v>0.99</v>
+      </c>
+      <c r="M428">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="429" spans="1:13">
+      <c r="A429" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B429" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C429" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D429" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E429" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F429">
+        <v>9</v>
+      </c>
+      <c r="G429">
+        <v>2</v>
+      </c>
+      <c r="H429" t="s">
+        <v>190</v>
+      </c>
+      <c r="I429">
+        <v>0.85</v>
+      </c>
+      <c r="J429">
+        <v>1.04</v>
+      </c>
+      <c r="K429" t="s">
+        <v>444</v>
+      </c>
+      <c r="L429">
+        <v>1.01</v>
+      </c>
+      <c r="M429">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="430" spans="1:13">
+      <c r="A430" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B430" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C430" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D430" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E430" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F430">
+        <v>3</v>
+      </c>
+      <c r="G430">
+        <v>9</v>
+      </c>
+      <c r="H430" t="s">
+        <v>190</v>
+      </c>
+      <c r="I430">
+        <v>0.94</v>
+      </c>
+      <c r="J430">
+        <v>0.95</v>
+      </c>
+      <c r="K430" t="s">
+        <v>445</v>
+      </c>
+      <c r="L430">
+        <v>0.99</v>
+      </c>
+      <c r="M430">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="431" spans="1:13">
+      <c r="A431" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B431" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C431" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D431" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E431" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F431">
+        <v>3</v>
+      </c>
+      <c r="G431">
+        <v>7</v>
+      </c>
+      <c r="H431" t="s">
+        <v>34</v>
+      </c>
+      <c r="I431">
+        <v>0.82</v>
+      </c>
+      <c r="J431">
+        <v>1</v>
+      </c>
+      <c r="K431">
+        <v>2.5</v>
+      </c>
+      <c r="L431">
+        <v>1</v>
+      </c>
+      <c r="M431">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="432" spans="1:13">
+      <c r="A432" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B432" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C432" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D432" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E432" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F432">
+        <v>4</v>
+      </c>
+      <c r="G432">
+        <v>3</v>
+      </c>
+      <c r="H432" t="s">
+        <v>166</v>
+      </c>
+      <c r="I432">
+        <v>0.95</v>
+      </c>
+      <c r="J432">
+        <v>0.87</v>
+      </c>
+      <c r="K432">
+        <v>3.5</v>
+      </c>
+      <c r="L432">
+        <v>0.88</v>
+      </c>
+      <c r="M432">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="433" spans="1:13">
+      <c r="A433" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B433" s="5">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="C433" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D433" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E433" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F433">
+        <v>3</v>
+      </c>
+      <c r="G433">
+        <v>15</v>
+      </c>
+      <c r="H433" t="s">
+        <v>26</v>
+      </c>
+      <c r="I433">
+        <v>0.91</v>
+      </c>
+      <c r="J433">
+        <v>0.91</v>
+      </c>
+      <c r="K433" t="s">
+        <v>444</v>
+      </c>
+      <c r="L433">
+        <v>0.88</v>
+      </c>
+      <c r="M433">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="434" spans="1:13">
+      <c r="A434" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B434" s="5">
+        <v>0.0625</v>
+      </c>
+      <c r="C434" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D434" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E434" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F434">
+        <v>1</v>
+      </c>
+      <c r="G434">
+        <v>2</v>
+      </c>
+      <c r="H434" t="s">
+        <v>222</v>
+      </c>
+      <c r="I434">
+        <v>0.8</v>
+      </c>
+      <c r="J434">
+        <v>1.02</v>
+      </c>
+      <c r="K434" t="s">
+        <v>444</v>
+      </c>
+      <c r="L434">
+        <v>0.8</v>
+      </c>
+      <c r="M434">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:13">
+      <c r="A435" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B435" s="5">
+        <v>0.0729166666666667</v>
+      </c>
+      <c r="C435" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D435" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E435" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F435">
+        <v>3</v>
+      </c>
+      <c r="G435">
+        <v>6</v>
+      </c>
+      <c r="H435" t="s">
+        <v>166</v>
+      </c>
+      <c r="I435">
+        <v>0.9</v>
+      </c>
+      <c r="J435">
+        <v>0.92</v>
+      </c>
+      <c r="K435">
+        <v>2.5</v>
+      </c>
+      <c r="L435">
+        <v>0.83</v>
+      </c>
+      <c r="M435">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="436" spans="1:13">
+      <c r="A436" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B436" s="5">
+        <v>0.0729166666666667</v>
+      </c>
+      <c r="C436" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D436" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E436" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F436">
+        <v>6</v>
+      </c>
+      <c r="G436">
+        <v>4</v>
+      </c>
+      <c r="H436" t="s">
+        <v>39</v>
+      </c>
+      <c r="I436">
+        <v>0.92</v>
+      </c>
+      <c r="J436">
+        <v>0.9</v>
+      </c>
+      <c r="K436">
+        <v>2</v>
+      </c>
+      <c r="L436">
+        <v>0.76</v>
+      </c>
+      <c r="M436">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="437" spans="1:13">
+      <c r="A437" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B437" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C437" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D437" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E437" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F437">
+        <v>3</v>
+      </c>
+      <c r="G437">
+        <v>10</v>
+      </c>
+      <c r="H437" t="s">
+        <v>166</v>
+      </c>
+      <c r="I437">
+        <v>0.9</v>
+      </c>
+      <c r="J437">
+        <v>0.92</v>
+      </c>
+      <c r="K437" t="s">
+        <v>444</v>
+      </c>
+      <c r="L437">
+        <v>0.94</v>
+      </c>
+      <c r="M437">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="438" spans="1:13">
+      <c r="A438" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B438" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C438" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D438" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E438" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="F438">
+        <v>6</v>
+      </c>
+      <c r="G438">
+        <v>2</v>
+      </c>
+      <c r="H438" t="s">
+        <v>161</v>
+      </c>
+      <c r="I438">
+        <v>0.8</v>
+      </c>
+      <c r="J438">
+        <v>1.09</v>
+      </c>
+      <c r="K438" t="s">
+        <v>442</v>
+      </c>
+      <c r="L438">
+        <v>0.95</v>
+      </c>
+      <c r="M438">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="439" spans="1:13">
+      <c r="A439" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B439" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C439" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D439" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E439" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F439">
+        <v>12</v>
+      </c>
+      <c r="G439">
+        <v>1</v>
+      </c>
+      <c r="H439" t="s">
+        <v>39</v>
+      </c>
+      <c r="I439">
+        <v>0.98</v>
+      </c>
+      <c r="J439">
+        <v>0.91</v>
+      </c>
+      <c r="K439">
+        <v>2.5</v>
+      </c>
+      <c r="L439">
+        <v>0.95</v>
+      </c>
+      <c r="M439">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="440" spans="1:13">
+      <c r="A440" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B440" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C440" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D440" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E440" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F440">
+        <v>2</v>
+      </c>
+      <c r="G440">
+        <v>2</v>
+      </c>
+      <c r="H440" t="s">
+        <v>34</v>
+      </c>
+      <c r="I440">
+        <v>0.97</v>
+      </c>
+      <c r="J440">
+        <v>0.85</v>
+      </c>
+      <c r="K440" t="s">
+        <v>444</v>
+      </c>
+      <c r="L440">
+        <v>0.97</v>
+      </c>
+      <c r="M440">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="441" spans="1:13">
+      <c r="A441" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B441" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C441" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D441" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E441" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F441">
+        <v>2</v>
+      </c>
+      <c r="G441">
+        <v>1</v>
+      </c>
+      <c r="H441" t="s">
+        <v>26</v>
+      </c>
+      <c r="I441">
+        <v>0.93</v>
+      </c>
+      <c r="J441">
+        <v>0.89</v>
+      </c>
+      <c r="K441" t="s">
+        <v>444</v>
+      </c>
+      <c r="L441">
+        <v>0.99</v>
+      </c>
+      <c r="M441">
+        <v>0.81</v>
+      </c>
+    </row>
+    <row r="442" spans="1:13">
+      <c r="A442" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B442" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C442" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D442" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E442" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F442">
+        <v>11</v>
+      </c>
+      <c r="G442">
+        <v>2</v>
+      </c>
+      <c r="H442" t="s">
+        <v>34</v>
+      </c>
+      <c r="I442">
+        <v>0.8</v>
+      </c>
+      <c r="J442">
+        <v>1.02</v>
+      </c>
+      <c r="K442">
+        <v>3</v>
+      </c>
+      <c r="L442">
+        <v>0.87</v>
+      </c>
+      <c r="M442">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="443" spans="1:13">
+      <c r="A443" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B443" s="5">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="C443" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D443" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E443" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F443">
+        <v>1</v>
+      </c>
+      <c r="G443">
+        <v>3</v>
+      </c>
+      <c r="H443" t="s">
+        <v>166</v>
+      </c>
+      <c r="I443">
+        <v>1.03</v>
+      </c>
+      <c r="J443">
+        <v>0.79</v>
+      </c>
+      <c r="K443">
+        <v>2.5</v>
+      </c>
+      <c r="L443">
+        <v>0.8</v>
+      </c>
+      <c r="M443">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:13">
+      <c r="A444" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B444" s="5">
+        <v>0.09375</v>
+      </c>
+      <c r="C444" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D444" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E444" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F444">
+        <v>4</v>
+      </c>
+      <c r="G444">
+        <v>5</v>
+      </c>
+      <c r="H444" t="s">
+        <v>222</v>
+      </c>
+      <c r="I444">
+        <v>0.84</v>
+      </c>
+      <c r="J444">
+        <v>0.98</v>
+      </c>
+      <c r="K444">
+        <v>3</v>
+      </c>
+      <c r="L444">
+        <v>1</v>
+      </c>
+      <c r="M444">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="445" spans="1:13">
+      <c r="A445" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B445" s="5">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="C445" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D445" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E445" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F445">
+        <v>7</v>
+      </c>
+      <c r="G445">
+        <v>3</v>
+      </c>
+      <c r="H445" t="s">
+        <v>403</v>
+      </c>
+      <c r="I445">
+        <v>0.84</v>
+      </c>
+      <c r="J445">
+        <v>0.98</v>
+      </c>
+      <c r="K445" t="s">
+        <v>445</v>
+      </c>
+      <c r="L445">
+        <v>0.93</v>
+      </c>
+      <c r="M445">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="446" spans="1:13">
+      <c r="A446" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B446" s="5">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="C446" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D446" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E446" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F446">
+        <v>3</v>
+      </c>
+      <c r="G446">
+        <v>7</v>
+      </c>
+      <c r="H446" t="s">
+        <v>166</v>
+      </c>
+      <c r="I446">
+        <v>0.84</v>
+      </c>
+      <c r="J446">
+        <v>0.98</v>
+      </c>
+      <c r="K446" t="s">
+        <v>442</v>
+      </c>
+      <c r="L446">
+        <v>0.95</v>
+      </c>
+      <c r="M446">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="447" spans="1:13">
+      <c r="A447" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B447" s="5">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="C447" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D447" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E447" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F447">
+        <v>1</v>
+      </c>
+      <c r="G447">
+        <v>4</v>
+      </c>
+      <c r="H447" t="s">
+        <v>161</v>
+      </c>
+      <c r="I447">
+        <v>0.93</v>
+      </c>
+      <c r="J447">
+        <v>0.89</v>
+      </c>
+      <c r="K447">
+        <v>2.5</v>
+      </c>
+      <c r="L447">
+        <v>0.81</v>
+      </c>
+      <c r="M447">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="448" spans="1:13">
+      <c r="A448" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B448" s="5">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="C448" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D448" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E448" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F448">
+        <v>3</v>
+      </c>
+      <c r="G448">
+        <v>10</v>
+      </c>
+      <c r="H448" t="s">
+        <v>178</v>
+      </c>
+      <c r="I448">
+        <v>0.77</v>
+      </c>
+      <c r="J448">
+        <v>1.05</v>
+      </c>
+      <c r="K448">
+        <v>2.5</v>
+      </c>
+      <c r="L448">
+        <v>0.85</v>
+      </c>
+      <c r="M448">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="449" spans="1:13">
+      <c r="A449" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B449" s="5">
+        <v>0.104166666666667</v>
+      </c>
+      <c r="C449" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D449" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E449" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F449">
+        <v>4</v>
+      </c>
+      <c r="G449">
+        <v>6</v>
+      </c>
+      <c r="H449" t="s">
+        <v>190</v>
+      </c>
+      <c r="I449">
+        <v>0.85</v>
+      </c>
+      <c r="J449">
+        <v>0.97</v>
+      </c>
+      <c r="K449">
+        <v>2.5</v>
+      </c>
+      <c r="L449">
+        <v>1.01</v>
+      </c>
+      <c r="M449">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="450" spans="1:13">
+      <c r="A450" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B450" s="5">
+        <v>0.114583333333333</v>
+      </c>
+      <c r="C450" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D450" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E450" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F450">
+        <v>4</v>
+      </c>
+      <c r="G450">
+        <v>1</v>
+      </c>
+      <c r="H450" t="s">
+        <v>161</v>
+      </c>
+      <c r="I450">
+        <v>0.81</v>
+      </c>
+      <c r="J450">
+        <v>1.01</v>
+      </c>
+      <c r="K450" t="s">
+        <v>444</v>
+      </c>
+      <c r="L450">
+        <v>0.8</v>
+      </c>
+      <c r="M450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:13">
+      <c r="A451" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B451" s="5">
+        <v>0.114583333333333</v>
+      </c>
+      <c r="C451" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D451" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E451" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F451">
+        <v>9</v>
+      </c>
+      <c r="G451">
+        <v>2</v>
+      </c>
+      <c r="H451" t="s">
+        <v>190</v>
+      </c>
+      <c r="I451">
+        <v>0.85</v>
+      </c>
+      <c r="J451">
+        <v>0.97</v>
+      </c>
+      <c r="K451" t="s">
+        <v>444</v>
+      </c>
+      <c r="L451">
+        <v>1</v>
+      </c>
+      <c r="M451">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="452" spans="1:13">
+      <c r="A452" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B452" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C452" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D452" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="E452" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="F452">
+        <v>8</v>
+      </c>
+      <c r="G452">
+        <v>14</v>
+      </c>
+      <c r="H452" t="s">
+        <v>161</v>
+      </c>
+      <c r="I452">
+        <v>0.93</v>
+      </c>
+      <c r="J452">
+        <v>0.96</v>
+      </c>
+      <c r="K452" t="s">
+        <v>442</v>
+      </c>
+      <c r="L452">
+        <v>1.06</v>
+      </c>
+      <c r="M452">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="453" spans="1:13">
+      <c r="A453" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B453" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C453" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D453" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E453" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F453">
+        <v>6</v>
+      </c>
+      <c r="G453">
+        <v>3</v>
+      </c>
+      <c r="H453" t="s">
+        <v>65</v>
+      </c>
+      <c r="I453">
+        <v>1.09</v>
+      </c>
+      <c r="J453">
+        <v>0.79</v>
+      </c>
+      <c r="K453">
+        <v>2.5</v>
+      </c>
+      <c r="L453">
+        <v>0.96</v>
+      </c>
+      <c r="M453">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="454" spans="1:13">
+      <c r="A454" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B454" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C454" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D454" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E454" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F454">
+        <v>10</v>
+      </c>
+      <c r="G454">
+        <v>8</v>
+      </c>
+      <c r="H454" t="s">
+        <v>190</v>
+      </c>
+      <c r="I454">
+        <v>1.01</v>
+      </c>
+      <c r="J454">
+        <v>0.81</v>
+      </c>
+      <c r="K454">
+        <v>2.5</v>
+      </c>
+      <c r="L454">
+        <v>0.97</v>
+      </c>
+      <c r="M454">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="455" spans="1:13">
+      <c r="A455" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B455" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C455" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D455" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E455" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F455">
+        <v>11</v>
+      </c>
+      <c r="G455">
+        <v>4</v>
+      </c>
+      <c r="H455" t="s">
+        <v>40</v>
+      </c>
+      <c r="I455">
+        <v>0.9</v>
+      </c>
+      <c r="J455">
+        <v>0.92</v>
+      </c>
+      <c r="K455" t="s">
+        <v>442</v>
+      </c>
+      <c r="L455">
+        <v>0.84</v>
+      </c>
+      <c r="M455">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="456" spans="1:13">
+      <c r="A456" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B456" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C456" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D456" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E456" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F456">
+        <v>7</v>
+      </c>
+      <c r="G456">
+        <v>11</v>
+      </c>
+      <c r="H456" t="s">
+        <v>9</v>
+      </c>
+      <c r="I456">
+        <v>0.88</v>
+      </c>
+      <c r="J456">
+        <v>0.94</v>
+      </c>
+      <c r="K456" t="s">
+        <v>442</v>
+      </c>
+      <c r="L456">
+        <v>0.83</v>
+      </c>
+      <c r="M456">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="457" spans="1:13">
+      <c r="A457" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B457" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C457" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D457" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E457" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F457">
+        <v>6</v>
+      </c>
+      <c r="G457">
+        <v>18</v>
+      </c>
+      <c r="H457" t="s">
+        <v>39</v>
+      </c>
+      <c r="I457">
+        <v>0.97</v>
+      </c>
+      <c r="J457">
+        <v>0.85</v>
+      </c>
+      <c r="K457" t="s">
+        <v>442</v>
+      </c>
+      <c r="L457">
+        <v>0.8</v>
+      </c>
+      <c r="M457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:13">
+      <c r="A458" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B458" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C458" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D458" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E458" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F458">
+        <v>11</v>
+      </c>
+      <c r="G458">
+        <v>1</v>
+      </c>
+      <c r="H458" t="s">
+        <v>161</v>
+      </c>
+      <c r="I458">
+        <v>1</v>
+      </c>
+      <c r="J458">
+        <v>0.82</v>
+      </c>
+      <c r="K458" t="s">
+        <v>442</v>
+      </c>
+      <c r="L458">
+        <v>1.05</v>
+      </c>
+      <c r="M458">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="459" spans="1:13">
+      <c r="A459" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B459" s="5">
+        <v>0.125</v>
+      </c>
+      <c r="C459" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D459" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E459" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F459">
+        <v>6</v>
+      </c>
+      <c r="G459">
+        <v>10</v>
+      </c>
+      <c r="H459" t="s">
+        <v>403</v>
+      </c>
+      <c r="I459">
+        <v>0.95</v>
+      </c>
+      <c r="J459">
+        <v>0.94</v>
+      </c>
+      <c r="K459">
+        <v>3.5</v>
+      </c>
+      <c r="L459">
+        <v>1.01</v>
+      </c>
+      <c r="M459">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="460" spans="1:13">
+      <c r="A460" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B460" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C460" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D460" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E460" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F460">
+        <v>2</v>
+      </c>
+      <c r="G460">
+        <v>14</v>
+      </c>
+      <c r="H460" t="s">
+        <v>161</v>
+      </c>
+      <c r="I460">
+        <v>1.01</v>
+      </c>
+      <c r="J460">
+        <v>0.88</v>
+      </c>
+      <c r="K460" t="s">
+        <v>442</v>
+      </c>
+      <c r="L460">
+        <v>0.85</v>
+      </c>
+      <c r="M460">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="461" spans="1:13">
+      <c r="A461" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B461" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="C461" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D461" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E461" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F461">
+        <v>6</v>
+      </c>
+      <c r="G461">
+        <v>19</v>
+      </c>
+      <c r="H461" t="s">
+        <v>161</v>
+      </c>
+      <c r="I461">
+        <v>0.88</v>
+      </c>
+      <c r="J461">
+        <v>1.01</v>
+      </c>
+      <c r="K461" t="s">
+        <v>442</v>
+      </c>
+      <c r="L461">
+        <v>1.07</v>
+      </c>
+      <c r="M461">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="462" spans="1:13">
+      <c r="A462" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B462" s="5">
+        <v>0.270833333333333</v>
+      </c>
+      <c r="C462" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D462" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E462" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F462">
+        <v>8</v>
+      </c>
+      <c r="G462">
+        <v>9</v>
+      </c>
+      <c r="H462" t="s">
+        <v>161</v>
+      </c>
+      <c r="I462">
+        <v>1.12</v>
+      </c>
+      <c r="J462">
+        <v>0.78</v>
+      </c>
+      <c r="K462" t="s">
+        <v>442</v>
+      </c>
+      <c r="L462">
+        <v>1.06</v>
+      </c>
+      <c r="M462">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="463" spans="1:13">
+      <c r="A463" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B463" s="5">
+        <v>0.3125</v>
+      </c>
+      <c r="C463" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D463" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E463" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F463">
+        <v>7</v>
+      </c>
+      <c r="G463">
+        <v>19</v>
+      </c>
+      <c r="H463" t="s">
+        <v>34</v>
+      </c>
+      <c r="I463">
+        <v>1.08</v>
+      </c>
+      <c r="J463">
+        <v>0.81</v>
+      </c>
+      <c r="K463" t="s">
+        <v>442</v>
+      </c>
+      <c r="L463">
+        <v>0.88</v>
+      </c>
+      <c r="M463">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="464" spans="1:13">
+      <c r="A464" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B464" s="5">
+        <v>0.350694444444444</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D464" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E464" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F464">
+        <v>15</v>
+      </c>
+      <c r="G464">
+        <v>6</v>
+      </c>
+      <c r="H464" t="s">
+        <v>40</v>
+      </c>
+      <c r="I464">
+        <v>0.88</v>
+      </c>
+      <c r="J464">
+        <v>1</v>
+      </c>
+      <c r="K464">
+        <v>3</v>
+      </c>
+      <c r="L464">
+        <v>0.83</v>
+      </c>
+      <c r="M464">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="465" spans="1:13">
+      <c r="A465" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B465" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C465" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D465" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E465" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F465">
+        <v>11</v>
+      </c>
+      <c r="G465">
+        <v>16</v>
+      </c>
+      <c r="H465" t="s">
+        <v>525</v>
+      </c>
+      <c r="I465">
+        <v>0.99</v>
+      </c>
+      <c r="J465">
+        <v>0.9</v>
+      </c>
+      <c r="K465" t="s">
+        <v>443</v>
+      </c>
+      <c r="L465">
+        <v>0.94</v>
+      </c>
+      <c r="M465">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="466" spans="1:13">
+      <c r="A466" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B466" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C466" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D466" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E466" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F466">
+        <v>8</v>
+      </c>
+      <c r="G466">
+        <v>11</v>
+      </c>
+      <c r="H466" t="s">
+        <v>65</v>
+      </c>
+      <c r="I466">
+        <v>0.92</v>
+      </c>
+      <c r="J466">
+        <v>0.9</v>
+      </c>
+      <c r="K466" t="s">
+        <v>442</v>
+      </c>
+      <c r="L466">
+        <v>1.01</v>
+      </c>
+      <c r="M466">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="467" spans="1:13">
+      <c r="A467" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B467" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C467" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D467" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E467" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F467">
+        <v>11</v>
+      </c>
+      <c r="G467">
+        <v>28</v>
+      </c>
+      <c r="H467" t="s">
+        <v>164</v>
+      </c>
+      <c r="I467">
+        <v>0.92</v>
+      </c>
+      <c r="J467">
+        <v>0.9</v>
+      </c>
+      <c r="K467" t="s">
+        <v>442</v>
+      </c>
+      <c r="L467">
+        <v>0.95</v>
+      </c>
+      <c r="M467">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="468" spans="1:13">
+      <c r="A468" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B468" s="5">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="C468" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D468" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E468" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F468">
+        <v>13</v>
+      </c>
+      <c r="G468">
+        <v>1</v>
+      </c>
+      <c r="H468" t="s">
+        <v>65</v>
+      </c>
+      <c r="I468">
+        <v>0.94</v>
+      </c>
+      <c r="J468">
+        <v>0.94</v>
+      </c>
+      <c r="K468">
+        <v>2</v>
+      </c>
+      <c r="L468">
+        <v>1.03</v>
+      </c>
+      <c r="M468">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="469" spans="1:13">
+      <c r="A469" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B469" s="5">
+        <v>0.361111111111111</v>
+      </c>
+      <c r="C469" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D469" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E469" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F469">
+        <v>9</v>
+      </c>
+      <c r="G469">
+        <v>15</v>
+      </c>
+      <c r="H469" t="s">
+        <v>166</v>
+      </c>
+      <c r="I469">
+        <v>1.02</v>
+      </c>
+      <c r="J469">
+        <v>0.86</v>
+      </c>
+      <c r="K469" t="s">
+        <v>444</v>
+      </c>
+      <c r="L469">
+        <v>0.89</v>
+      </c>
+      <c r="M469">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="470" spans="1:13">
+      <c r="A470" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B470" s="5">
+        <v>0.402777777777778</v>
+      </c>
+      <c r="C470" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D470" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="E470" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F470">
+        <v>8</v>
+      </c>
+      <c r="G470">
+        <v>3</v>
+      </c>
+      <c r="H470" t="s">
+        <v>65</v>
+      </c>
+      <c r="I470">
+        <v>1.05</v>
+      </c>
+      <c r="J470">
+        <v>0.83</v>
+      </c>
+      <c r="K470" t="s">
+        <v>444</v>
+      </c>
+      <c r="L470">
+        <v>0.87</v>
+      </c>
+      <c r="M470">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:13">
+      <c r="A471" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B471" s="5">
+        <v>0.402777777777778</v>
+      </c>
+      <c r="C471" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D471" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E471" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F471">
+        <v>7</v>
+      </c>
+      <c r="G471">
+        <v>5</v>
+      </c>
+      <c r="H471" t="s">
+        <v>39</v>
+      </c>
+      <c r="I471">
+        <v>0.94</v>
+      </c>
+      <c r="J471">
+        <v>0.94</v>
+      </c>
+      <c r="K471">
+        <v>3</v>
+      </c>
+      <c r="L471">
+        <v>0.86</v>
+      </c>
+      <c r="M471">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="472" spans="1:13">
+      <c r="A472" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B472" s="5">
+        <v>0.402777777777778</v>
+      </c>
+      <c r="C472" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D472" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E472" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F472">
+        <v>11</v>
+      </c>
+      <c r="G472">
+        <v>14</v>
+      </c>
+      <c r="H472" t="s">
+        <v>34</v>
+      </c>
+      <c r="I472">
+        <v>1.04</v>
+      </c>
+      <c r="J472">
+        <v>0.84</v>
+      </c>
+      <c r="K472">
+        <v>3</v>
+      </c>
+      <c r="L472">
+        <v>0.83</v>
+      </c>
+      <c r="M472">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="473" spans="1:13">
+      <c r="A473" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B473" s="5">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="C473" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D473" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="E473" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="F473">
+        <v>13</v>
+      </c>
+      <c r="G473">
+        <v>4</v>
+      </c>
+      <c r="H473" t="s">
+        <v>161</v>
+      </c>
+      <c r="I473">
+        <v>1</v>
+      </c>
+      <c r="J473">
+        <v>0.88</v>
+      </c>
+      <c r="K473" t="s">
+        <v>445</v>
+      </c>
+      <c r="L473">
+        <v>0.94</v>
+      </c>
+      <c r="M473">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="474" spans="1:13">
+      <c r="A474" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B474" s="5">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="C474" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D474" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E474" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F474">
+        <v>10</v>
+      </c>
+      <c r="G474">
+        <v>12</v>
+      </c>
+      <c r="H474" t="s">
+        <v>161</v>
+      </c>
+      <c r="I474">
+        <v>0.87</v>
+      </c>
+      <c r="J474">
+        <v>1.01</v>
+      </c>
+      <c r="K474">
+        <v>3.5</v>
+      </c>
+      <c r="L474">
+        <v>1</v>
+      </c>
+      <c r="M474">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="475" spans="1:13">
+      <c r="A475" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B475" s="5">
+        <v>0.444444444444444</v>
+      </c>
+      <c r="C475" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D475" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E475" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F475">
+        <v>1</v>
+      </c>
+      <c r="G475">
+        <v>2</v>
+      </c>
+      <c r="H475" t="s">
+        <v>34</v>
+      </c>
+      <c r="I475">
+        <v>0.95</v>
+      </c>
+      <c r="J475">
+        <v>0.93</v>
+      </c>
+      <c r="K475">
+        <v>3</v>
+      </c>
+      <c r="L475">
+        <v>0.91</v>
+      </c>
+      <c r="M475">
+        <v>0.96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E402" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:E402">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A2:E419" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:E419">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -12472,7 +14849,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14.875"/>
@@ -12781,7 +15158,7 @@
         <v>417</v>
       </c>
       <c r="E18" t="s">
-        <v>492</v>
+        <v>546</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -12798,7 +15175,7 @@
         <v>418</v>
       </c>
       <c r="E19" t="s">
-        <v>493</v>
+        <v>547</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -12815,7 +15192,7 @@
         <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>494</v>
+        <v>548</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -12832,7 +15209,7 @@
         <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>495</v>
+        <v>549</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -12849,7 +15226,7 @@
         <v>239</v>
       </c>
       <c r="E22" t="s">
-        <v>496</v>
+        <v>550</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -12866,7 +15243,7 @@
         <v>421</v>
       </c>
       <c r="E23" t="s">
-        <v>497</v>
+        <v>551</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -12883,7 +15260,7 @@
         <v>427</v>
       </c>
       <c r="E24" t="s">
-        <v>498</v>
+        <v>552</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -12900,7 +15277,7 @@
         <v>429</v>
       </c>
       <c r="E25" t="s">
-        <v>499</v>
+        <v>553</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -12917,7 +15294,7 @@
         <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>500</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -12925,10 +15302,10 @@
         <v>46246</v>
       </c>
       <c r="B27" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C27" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D27" t="s">
         <v>195</v>
@@ -12993,13 +15370,13 @@
         <v>46247</v>
       </c>
       <c r="B31" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C31" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="D31" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E31" t="s">
         <v>161</v>
@@ -13101,7 +15478,7 @@
         <v>416</v>
       </c>
       <c r="D37" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E37" t="s">
         <v>222</v>
@@ -13149,10 +15526,10 @@
         <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D40" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="E40" t="s">
         <v>39</v>
@@ -13220,7 +15597,7 @@
         <v>368</v>
       </c>
       <c r="D44" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="E44" t="s">
         <v>161</v>
@@ -13302,7 +15679,7 @@
         <v>309</v>
       </c>
       <c r="C49" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D49" t="s">
         <v>363</v>
@@ -13319,7 +15696,7 @@
         <v>309</v>
       </c>
       <c r="C50" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="D50" t="s">
         <v>310</v>
@@ -13336,7 +15713,7 @@
         <v>422</v>
       </c>
       <c r="C51" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D51" t="s">
         <v>430</v>
@@ -13424,7 +15801,7 @@
         <v>195</v>
       </c>
       <c r="D56" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E56" t="s">
         <v>39</v>
@@ -13475,7 +15852,7 @@
         <v>169</v>
       </c>
       <c r="D59" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E59" t="s">
         <v>164</v>
@@ -13492,7 +15869,7 @@
         <v>362</v>
       </c>
       <c r="D60" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="E60" t="s">
         <v>164</v>
@@ -13591,7 +15968,7 @@
         <v>170</v>
       </c>
       <c r="C66" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="D66" t="s">
         <v>172</v>
@@ -13628,7 +16005,7 @@
         <v>413</v>
       </c>
       <c r="D68" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E68" t="s">
         <v>39</v>
@@ -13645,7 +16022,7 @@
         <v>267</v>
       </c>
       <c r="D69" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="E69" t="s">
         <v>34</v>
@@ -13659,10 +16036,10 @@
         <v>170</v>
       </c>
       <c r="C70" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D70" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E70" t="s">
         <v>65</v>
@@ -13673,13 +16050,13 @@
         <v>46251</v>
       </c>
       <c r="B71" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C71" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D71" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="E71" t="s">
         <v>161</v>
@@ -13730,7 +16107,7 @@
         <v>186</v>
       </c>
       <c r="D74" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E74" t="s">
         <v>164</v>
@@ -13741,13 +16118,13 @@
         <v>46252</v>
       </c>
       <c r="B75" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C75" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D75" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E75" t="s">
         <v>65</v>
@@ -13758,13 +16135,13 @@
         <v>46252</v>
       </c>
       <c r="B76" t="s">
+        <v>474</v>
+      </c>
+      <c r="C76" t="s">
+        <v>477</v>
+      </c>
+      <c r="D76" t="s">
         <v>478</v>
-      </c>
-      <c r="C76" t="s">
-        <v>481</v>
-      </c>
-      <c r="D76" t="s">
-        <v>482</v>
       </c>
       <c r="E76" t="s">
         <v>164</v>
@@ -13775,13 +16152,13 @@
         <v>46252</v>
       </c>
       <c r="B77" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C77" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D77" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="E77" t="s">
         <v>190</v>
@@ -13795,10 +16172,10 @@
         <v>158</v>
       </c>
       <c r="C78" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D78" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E78" t="s">
         <v>166</v>
@@ -13866,7 +16243,7 @@
         <v>103</v>
       </c>
       <c r="D82" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="E82" t="s">
         <v>9</v>
@@ -13900,7 +16277,7 @@
         <v>102</v>
       </c>
       <c r="D84" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E84" t="s">
         <v>199</v>
@@ -13937,7 +16314,7 @@
         <v>52</v>
       </c>
       <c r="E86" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -13954,7 +16331,7 @@
         <v>110</v>
       </c>
       <c r="E87" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -13968,10 +16345,741 @@
         <v>68</v>
       </c>
       <c r="D88" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E88" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B89" t="s">
+        <v>139</v>
+      </c>
+      <c r="C89" t="s">
+        <v>187</v>
+      </c>
+      <c r="D89" t="s">
+        <v>142</v>
+      </c>
+      <c r="E89" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B90" t="s">
+        <v>139</v>
+      </c>
+      <c r="C90" t="s">
+        <v>200</v>
+      </c>
+      <c r="D90" t="s">
+        <v>193</v>
+      </c>
+      <c r="E90" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B91" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91" t="s">
+        <v>98</v>
+      </c>
+      <c r="D91" t="s">
+        <v>218</v>
+      </c>
+      <c r="E91" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B92" t="s">
+        <v>181</v>
+      </c>
+      <c r="C92" t="s">
+        <v>151</v>
+      </c>
+      <c r="D92" t="s">
+        <v>221</v>
+      </c>
+      <c r="E92" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B93" t="s">
+        <v>181</v>
+      </c>
+      <c r="C93" t="s">
+        <v>488</v>
+      </c>
+      <c r="D93" t="s">
+        <v>192</v>
+      </c>
+      <c r="E93" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B94" t="s">
+        <v>490</v>
+      </c>
+      <c r="C94" t="s">
+        <v>491</v>
+      </c>
+      <c r="D94" t="s">
+        <v>492</v>
+      </c>
+      <c r="E94" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B95" t="s">
+        <v>139</v>
+      </c>
+      <c r="C95" t="s">
+        <v>217</v>
+      </c>
+      <c r="D95" t="s">
+        <v>191</v>
+      </c>
+      <c r="E95" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B96" t="s">
+        <v>139</v>
+      </c>
+      <c r="C96" t="s">
+        <v>117</v>
+      </c>
+      <c r="D96" t="s">
+        <v>106</v>
+      </c>
+      <c r="E96" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B97" t="s">
+        <v>139</v>
+      </c>
+      <c r="C97" t="s">
+        <v>493</v>
+      </c>
+      <c r="D97" t="s">
+        <v>140</v>
+      </c>
+      <c r="E97" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B98" t="s">
+        <v>139</v>
+      </c>
+      <c r="C98" t="s">
+        <v>116</v>
+      </c>
+      <c r="D98" t="s">
+        <v>179</v>
+      </c>
+      <c r="E98" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B99" t="s">
+        <v>181</v>
+      </c>
+      <c r="C99" t="s">
+        <v>252</v>
+      </c>
+      <c r="D99" t="s">
+        <v>250</v>
+      </c>
+      <c r="E99" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B100" t="s">
+        <v>181</v>
+      </c>
+      <c r="C100" t="s">
+        <v>245</v>
+      </c>
+      <c r="D100" t="s">
+        <v>229</v>
+      </c>
+      <c r="E100" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B101" t="s">
+        <v>181</v>
+      </c>
+      <c r="C101" t="s">
+        <v>212</v>
+      </c>
+      <c r="D101" t="s">
+        <v>494</v>
+      </c>
+      <c r="E101" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B102" t="s">
+        <v>181</v>
+      </c>
+      <c r="C102" t="s">
+        <v>495</v>
+      </c>
+      <c r="D102" t="s">
+        <v>223</v>
+      </c>
+      <c r="E102" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B103" t="s">
+        <v>181</v>
+      </c>
+      <c r="C103" t="s">
+        <v>237</v>
+      </c>
+      <c r="D103" t="s">
+        <v>86</v>
+      </c>
+      <c r="E103" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B104" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104" t="s">
+        <v>499</v>
+      </c>
+      <c r="D104" t="s">
+        <v>500</v>
+      </c>
+      <c r="E104" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B105" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" t="s">
+        <v>501</v>
+      </c>
+      <c r="D105" t="s">
+        <v>203</v>
+      </c>
+      <c r="E105" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B106" t="s">
+        <v>139</v>
+      </c>
+      <c r="C106" t="s">
+        <v>361</v>
+      </c>
+      <c r="D106" t="s">
+        <v>113</v>
+      </c>
+      <c r="E106" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B107" t="s">
+        <v>181</v>
+      </c>
+      <c r="C107" t="s">
+        <v>502</v>
+      </c>
+      <c r="D107" t="s">
+        <v>233</v>
+      </c>
+      <c r="E107" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B108" t="s">
+        <v>181</v>
+      </c>
+      <c r="C108" t="s">
+        <v>138</v>
+      </c>
+      <c r="D108" t="s">
+        <v>503</v>
+      </c>
+      <c r="E108" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B109" t="s">
+        <v>181</v>
+      </c>
+      <c r="C109" t="s">
+        <v>141</v>
+      </c>
+      <c r="D109" t="s">
+        <v>231</v>
+      </c>
+      <c r="E109" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B110" t="s">
+        <v>181</v>
+      </c>
+      <c r="C110" t="s">
+        <v>238</v>
+      </c>
+      <c r="D110" t="s">
+        <v>246</v>
+      </c>
+      <c r="E110" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B111" t="s">
+        <v>181</v>
+      </c>
+      <c r="C111" t="s">
+        <v>206</v>
+      </c>
+      <c r="D111" t="s">
+        <v>239</v>
+      </c>
+      <c r="E111" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B112" t="s">
+        <v>181</v>
+      </c>
+      <c r="C112" t="s">
+        <v>504</v>
+      </c>
+      <c r="D112" t="s">
+        <v>241</v>
+      </c>
+      <c r="E112" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B113" t="s">
+        <v>181</v>
+      </c>
+      <c r="C113" t="s">
+        <v>232</v>
+      </c>
+      <c r="D113" t="s">
+        <v>256</v>
+      </c>
+      <c r="E113" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B114" t="s">
+        <v>181</v>
+      </c>
+      <c r="C114" t="s">
+        <v>248</v>
+      </c>
+      <c r="D114" t="s">
+        <v>202</v>
+      </c>
+      <c r="E114" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B115" t="s">
+        <v>181</v>
+      </c>
+      <c r="C115" t="s">
+        <v>207</v>
+      </c>
+      <c r="D115" t="s">
+        <v>505</v>
+      </c>
+      <c r="E115" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B116" t="s">
+        <v>181</v>
+      </c>
+      <c r="C116" t="s">
+        <v>197</v>
+      </c>
+      <c r="D116" t="s">
+        <v>555</v>
+      </c>
+      <c r="E116" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B117" t="s">
+        <v>181</v>
+      </c>
+      <c r="C117" t="s">
+        <v>263</v>
+      </c>
+      <c r="D117" t="s">
+        <v>209</v>
+      </c>
+      <c r="E117" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B118" t="s">
+        <v>181</v>
+      </c>
+      <c r="C118" t="s">
+        <v>201</v>
+      </c>
+      <c r="D118" t="s">
+        <v>204</v>
+      </c>
+      <c r="E118" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B119" t="s">
+        <v>181</v>
+      </c>
+      <c r="C119" t="s">
+        <v>511</v>
+      </c>
+      <c r="D119" t="s">
+        <v>236</v>
+      </c>
+      <c r="E119" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B120" t="s">
+        <v>181</v>
+      </c>
+      <c r="C120" t="s">
+        <v>513</v>
+      </c>
+      <c r="D120" t="s">
+        <v>261</v>
+      </c>
+      <c r="E120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B121" t="s">
+        <v>181</v>
+      </c>
+      <c r="C121" t="s">
+        <v>226</v>
+      </c>
+      <c r="D121" t="s">
+        <v>227</v>
+      </c>
+      <c r="E121" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B122" t="s">
+        <v>181</v>
+      </c>
+      <c r="C122" t="s">
+        <v>165</v>
+      </c>
+      <c r="D122" t="s">
+        <v>109</v>
+      </c>
+      <c r="E122" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B123" t="s">
+        <v>139</v>
+      </c>
+      <c r="C123" t="s">
+        <v>262</v>
+      </c>
+      <c r="D123" t="s">
+        <v>136</v>
+      </c>
+      <c r="E123" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B124" t="s">
+        <v>470</v>
+      </c>
+      <c r="C124" t="s">
+        <v>506</v>
+      </c>
+      <c r="D124" t="s">
+        <v>507</v>
+      </c>
+      <c r="E124" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B125" t="s">
+        <v>508</v>
+      </c>
+      <c r="C125" t="s">
+        <v>509</v>
+      </c>
+      <c r="D125" t="s">
+        <v>510</v>
+      </c>
+      <c r="E125" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B126" t="s">
+        <v>556</v>
+      </c>
+      <c r="C126" t="s">
+        <v>557</v>
+      </c>
+      <c r="D126" t="s">
+        <v>104</v>
+      </c>
+      <c r="E126" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B127" t="s">
+        <v>556</v>
+      </c>
+      <c r="C127" t="s">
+        <v>559</v>
+      </c>
+      <c r="D127" t="s">
+        <v>560</v>
+      </c>
+      <c r="E127" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B128" t="s">
+        <v>496</v>
+      </c>
+      <c r="C128" t="s">
+        <v>561</v>
+      </c>
+      <c r="D128" t="s">
+        <v>498</v>
+      </c>
+      <c r="E128" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B129" t="s">
+        <v>452</v>
+      </c>
+      <c r="C129" t="s">
+        <v>526</v>
+      </c>
+      <c r="D129" t="s">
+        <v>527</v>
+      </c>
+      <c r="E129" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B130" t="s">
+        <v>452</v>
+      </c>
+      <c r="C130" t="s">
+        <v>528</v>
+      </c>
+      <c r="D130" t="s">
+        <v>529</v>
+      </c>
+      <c r="E130" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="1">
+        <v>46254</v>
+      </c>
+      <c r="B131" t="s">
+        <v>344</v>
+      </c>
+      <c r="C131" t="s">
+        <v>530</v>
+      </c>
+      <c r="D131" t="s">
+        <v>531</v>
+      </c>
+      <c r="E131" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
